--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ125"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137271106</v>
       </c>
       <c r="B9" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>137271124</v>
       </c>
       <c r="B11" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>137268894</v>
       </c>
       <c r="B13" t="n">
-        <v>87357</v>
+        <v>87367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137271097</v>
       </c>
       <c r="B14" t="n">
-        <v>87357</v>
+        <v>87367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137268895</v>
       </c>
       <c r="B16" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137268900</v>
       </c>
       <c r="B17" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137269999</v>
       </c>
       <c r="B18" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137270001</v>
       </c>
       <c r="B19" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137270004</v>
       </c>
       <c r="B20" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137270007</v>
       </c>
       <c r="B21" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137273093</v>
       </c>
       <c r="B22" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137273095</v>
       </c>
       <c r="B23" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137287620</v>
       </c>
       <c r="B24" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137291987</v>
       </c>
       <c r="B25" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137268891</v>
       </c>
       <c r="B26" t="n">
-        <v>90909</v>
+        <v>90919</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137268899</v>
       </c>
       <c r="B27" t="n">
-        <v>90909</v>
+        <v>90919</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137270003</v>
       </c>
       <c r="B30" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137291990</v>
       </c>
       <c r="B32" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137268897</v>
       </c>
       <c r="B34" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>137271107</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137271121</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>137271127</v>
       </c>
       <c r="B40" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>137273099</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137273105</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>137291988</v>
       </c>
       <c r="B43" t="n">
-        <v>89302</v>
+        <v>89312</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>137291989</v>
       </c>
       <c r="B66" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>137268893</v>
       </c>
       <c r="B98" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>137268896</v>
       </c>
       <c r="B99" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>137268902</v>
       </c>
       <c r="B100" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137270002</v>
       </c>
       <c r="B101" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>137271098</v>
       </c>
       <c r="B102" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>137271110</v>
       </c>
       <c r="B103" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>137271118</v>
       </c>
       <c r="B104" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>137273092</v>
       </c>
       <c r="B105" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>137273103</v>
       </c>
       <c r="B106" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12497,57 +12497,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>69178541</v>
+        <v>137313530</v>
       </c>
       <c r="B107" t="n">
-        <v>87346</v>
+        <v>87485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701531</v>
+        <v>701645</v>
       </c>
       <c r="R107" t="n">
-        <v>6360078</v>
+        <v>6359988</v>
       </c>
       <c r="S107" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12571,12 +12562,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12591,24 +12592,24 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178541</t>
+          <t>https://artportalen.se/Sighting/137313530</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>89804386</v>
+        <v>69178541</v>
       </c>
       <c r="B108" t="n">
         <v>87346</v>
@@ -12646,21 +12647,19 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701357</v>
+        <v>701531</v>
       </c>
       <c r="R108" t="n">
-        <v>6360028</v>
+        <v>6360078</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12679,17 +12678,17 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12698,34 +12697,33 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89804386</t>
+          <t>https://artportalen.se/Sighting/69178541</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137268901</v>
+        <v>89804386</v>
       </c>
       <c r="B109" t="n">
-        <v>87559</v>
+        <v>87346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12750,17 +12748,28 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701648</v>
+        <v>701357</v>
       </c>
       <c r="R109" t="n">
-        <v>6360091</v>
+        <v>6360028</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12782,27 +12791,17 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12818,27 +12817,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268901</t>
+          <t>https://artportalen.se/Sighting/89804386</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137271099</v>
+        <v>137268901</v>
       </c>
       <c r="B110" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12866,17 +12865,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701497</v>
+        <v>701648</v>
       </c>
       <c r="R110" t="n">
-        <v>6359942</v>
+        <v>6360091</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12905,7 +12904,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12915,7 +12914,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12924,33 +12923,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271099</t>
+          <t>https://artportalen.se/Sighting/137268901</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137271101</v>
+        <v>137271099</v>
       </c>
       <c r="B111" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12982,10 +12982,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>701511</v>
+        <v>701497</v>
       </c>
       <c r="R111" t="n">
-        <v>6359954</v>
+        <v>6359942</v>
       </c>
       <c r="S111" t="n">
         <v>7</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13053,16 +13053,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271101</t>
+          <t>https://artportalen.se/Sighting/137271099</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137271102</v>
+        <v>137271101</v>
       </c>
       <c r="B112" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13094,13 +13094,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701503</v>
+        <v>701511</v>
       </c>
       <c r="R112" t="n">
-        <v>6359960</v>
+        <v>6359954</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13165,16 +13165,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271102</t>
+          <t>https://artportalen.se/Sighting/137271101</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137271104</v>
+        <v>137271102</v>
       </c>
       <c r="B113" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13206,13 +13206,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701539</v>
+        <v>701503</v>
       </c>
       <c r="R113" t="n">
-        <v>6359971</v>
+        <v>6359960</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13277,16 +13277,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271104</t>
+          <t>https://artportalen.se/Sighting/137271102</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137271105</v>
+        <v>137271104</v>
       </c>
       <c r="B114" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>701536</v>
+        <v>701539</v>
       </c>
       <c r="R114" t="n">
-        <v>6359951</v>
+        <v>6359971</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13389,16 +13389,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271105</t>
+          <t>https://artportalen.se/Sighting/137271104</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137271111</v>
+        <v>137271105</v>
       </c>
       <c r="B115" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13430,13 +13430,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>701561</v>
+        <v>701536</v>
       </c>
       <c r="R115" t="n">
-        <v>6360029</v>
+        <v>6359951</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13501,16 +13501,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271111</t>
+          <t>https://artportalen.se/Sighting/137271105</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137271114</v>
+        <v>137271111</v>
       </c>
       <c r="B116" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13542,13 +13542,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>701604</v>
+        <v>701561</v>
       </c>
       <c r="R116" t="n">
-        <v>6360076</v>
+        <v>6360029</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13613,16 +13613,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271114</t>
+          <t>https://artportalen.se/Sighting/137271111</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137271120</v>
+        <v>137271114</v>
       </c>
       <c r="B117" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13654,10 +13654,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>701636</v>
+        <v>701604</v>
       </c>
       <c r="R117" t="n">
-        <v>6359977</v>
+        <v>6360076</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13725,16 +13725,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271120</t>
+          <t>https://artportalen.se/Sighting/137271114</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137271123</v>
+        <v>137271120</v>
       </c>
       <c r="B118" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>701680</v>
+        <v>701636</v>
       </c>
       <c r="R118" t="n">
-        <v>6359996</v>
+        <v>6359977</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13837,16 +13837,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271123</t>
+          <t>https://artportalen.se/Sighting/137271120</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137271125</v>
+        <v>137271123</v>
       </c>
       <c r="B119" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701684</v>
+        <v>701680</v>
       </c>
       <c r="R119" t="n">
-        <v>6359985</v>
+        <v>6359996</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13949,16 +13949,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271125</t>
+          <t>https://artportalen.se/Sighting/137271123</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137273090</v>
+        <v>137271125</v>
       </c>
       <c r="B120" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13986,14 +13986,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701447</v>
+        <v>701684</v>
       </c>
       <c r="R120" t="n">
-        <v>6359950</v>
+        <v>6359985</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14044,34 +14044,33 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273090</t>
+          <t>https://artportalen.se/Sighting/137271125</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137273096</v>
+        <v>137273090</v>
       </c>
       <c r="B121" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14103,10 +14102,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701577</v>
+        <v>701447</v>
       </c>
       <c r="R121" t="n">
-        <v>6360063</v>
+        <v>6359950</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14138,7 +14137,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14148,7 +14147,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14175,16 +14174,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273096</t>
+          <t>https://artportalen.se/Sighting/137273090</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137273098</v>
+        <v>137273096</v>
       </c>
       <c r="B122" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14216,10 +14215,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701552</v>
+        <v>701577</v>
       </c>
       <c r="R122" t="n">
-        <v>6360025</v>
+        <v>6360063</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14251,7 +14250,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14261,7 +14260,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14288,16 +14287,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273098</t>
+          <t>https://artportalen.se/Sighting/137273096</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137273100</v>
+        <v>137273098</v>
       </c>
       <c r="B123" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14329,10 +14328,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701602</v>
+        <v>701552</v>
       </c>
       <c r="R123" t="n">
-        <v>6359969</v>
+        <v>6360025</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14364,7 +14363,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14374,7 +14373,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14401,16 +14400,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273100</t>
+          <t>https://artportalen.se/Sighting/137273098</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137273104</v>
+        <v>137273100</v>
       </c>
       <c r="B124" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14442,10 +14441,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701659</v>
+        <v>701602</v>
       </c>
       <c r="R124" t="n">
-        <v>6360008</v>
+        <v>6359969</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14477,7 +14476,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14487,7 +14486,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14514,54 +14513,54 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273104</t>
+          <t>https://artportalen.se/Sighting/137273100</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137271117</v>
+        <v>137273104</v>
       </c>
       <c r="B125" t="n">
-        <v>87587</v>
+        <v>87569</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6052416</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701617</v>
+        <v>701659</v>
       </c>
       <c r="R125" t="n">
-        <v>6359978</v>
+        <v>6360008</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14590,7 +14589,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14600,7 +14599,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14609,22 +14608,135 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273104</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>137271117</v>
+      </c>
+      <c r="B126" t="n">
+        <v>87597</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>701617</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6359978</v>
+      </c>
+      <c r="S126" t="n">
+        <v>6</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271117</t>
         </is>
@@ -14756,6 +14868,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ126"/>
+  <dimension ref="A1:AZ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69178533</v>
+        <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87368</v>
+        <v>87417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,46 +1367,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701531</v>
+        <v>701629</v>
       </c>
       <c r="R8" t="n">
-        <v>6360078</v>
+        <v>6360017</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,12 +1424,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,33 +1438,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178533</t>
+          <t>https://artportalen.se/Sighting/137335983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137271106</v>
+        <v>69178533</v>
       </c>
       <c r="B9" t="n">
-        <v>87591</v>
+        <v>87368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,20 +1490,29 @@
           <t>Kytöv. &amp; al.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701544</v>
+        <v>701531</v>
       </c>
       <c r="R9" t="n">
-        <v>6359952</v>
+        <v>6360078</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,22 +1536,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,74 +1556,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271106</t>
+          <t>https://artportalen.se/Sighting/69178533</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69178538</v>
+        <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87289</v>
+        <v>87592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bon</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701531</v>
+        <v>701544</v>
       </c>
       <c r="R10" t="n">
-        <v>6360078</v>
+        <v>6359952</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,12 +1638,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,27 +1668,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178538</t>
+          <t>https://artportalen.se/Sighting/137271106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137271124</v>
+        <v>69178538</v>
       </c>
       <c r="B11" t="n">
-        <v>87512</v>
+        <v>87289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,20 +1713,29 @@
           <t>Bon</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701681</v>
+        <v>701531</v>
       </c>
       <c r="R11" t="n">
-        <v>6359991</v>
+        <v>6360078</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,22 +1759,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,79 +1779,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271124</t>
+          <t>https://artportalen.se/Sighting/69178538</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120308047</v>
+        <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>109837</v>
+        <v>87513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1489</v>
+        <v>473</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alvarstånds</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jacobaea vulgaris subsp. gotlandica</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Neuman) B. Nord.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701438</v>
+        <v>701681</v>
       </c>
       <c r="R12" t="n">
         <v>6359991</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,12 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,74 +1887,83 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308047</t>
+          <t>https://artportalen.se/Sighting/137271124</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137268894</v>
+        <v>120308047</v>
       </c>
       <c r="B13" t="n">
-        <v>87367</v>
+        <v>109837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1985</v>
+        <v>1489</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Alvarstånds</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Jacobaea vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Neuman) B. Nord.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701413</v>
+        <v>701438</v>
       </c>
       <c r="R13" t="n">
-        <v>6360072</v>
+        <v>6359991</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,22 +1987,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,31 +2003,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268894</t>
+          <t>https://artportalen.se/Sighting/120308047</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137271097</v>
+        <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87367</v>
+        <v>87368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,14 +2060,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701448</v>
+        <v>701413</v>
       </c>
       <c r="R14" t="n">
-        <v>6359921</v>
+        <v>6360072</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,74 +2124,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271097</t>
+          <t>https://artportalen.se/Sighting/137268894</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69178540</v>
+        <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87322</v>
+        <v>87368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701531</v>
+        <v>701448</v>
       </c>
       <c r="R15" t="n">
-        <v>6360078</v>
+        <v>6359921</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,12 +2206,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,27 +2236,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178540</t>
+          <t>https://artportalen.se/Sighting/137271097</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137268895</v>
+        <v>69178540</v>
       </c>
       <c r="B16" t="n">
-        <v>87545</v>
+        <v>87322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,20 +2281,29 @@
           <t>Fr.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701436</v>
+        <v>701531</v>
       </c>
       <c r="R16" t="n">
-        <v>6360088</v>
+        <v>6360078</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,22 +2327,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,27 +2347,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268895</t>
+          <t>https://artportalen.se/Sighting/69178540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137268900</v>
+        <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701650</v>
+        <v>701436</v>
       </c>
       <c r="R17" t="n">
-        <v>6360125</v>
+        <v>6360088</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,16 +2470,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268900</t>
+          <t>https://artportalen.se/Sighting/137268895</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137269999</v>
+        <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,14 +2507,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701431</v>
+        <v>701650</v>
       </c>
       <c r="R18" t="n">
-        <v>6359949</v>
+        <v>6360125</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,27 +2571,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137269999</t>
+          <t>https://artportalen.se/Sighting/137268900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137270001</v>
+        <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701464</v>
+        <v>701431</v>
       </c>
       <c r="R19" t="n">
-        <v>6359976</v>
+        <v>6359949</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2664,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,16 +2694,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270001</t>
+          <t>https://artportalen.se/Sighting/137269999</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137270004</v>
+        <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,13 +2735,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701538</v>
+        <v>701464</v>
       </c>
       <c r="R20" t="n">
-        <v>6359998</v>
+        <v>6359976</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,16 +2806,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270004</t>
+          <t>https://artportalen.se/Sighting/137270001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137270007</v>
+        <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,13 +2847,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701580</v>
+        <v>701538</v>
       </c>
       <c r="R21" t="n">
-        <v>6360056</v>
+        <v>6359998</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2888,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,16 +2918,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270007</t>
+          <t>https://artportalen.se/Sighting/137270004</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137273093</v>
+        <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701448</v>
+        <v>701580</v>
       </c>
       <c r="R22" t="n">
-        <v>6360112</v>
+        <v>6360056</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3000,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,27 +3019,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273093</t>
+          <t>https://artportalen.se/Sighting/137270007</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137273095</v>
+        <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701610</v>
+        <v>701448</v>
       </c>
       <c r="R23" t="n">
-        <v>6360170</v>
+        <v>6360112</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3112,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,16 +3142,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273095</t>
+          <t>https://artportalen.se/Sighting/137273093</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137287620</v>
+        <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3185,17 +3179,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701675</v>
+        <v>701610</v>
       </c>
       <c r="R24" t="n">
-        <v>6359988</v>
+        <v>6360170</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3219,22 +3213,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,27 +3243,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287620</t>
+          <t>https://artportalen.se/Sighting/137273095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137291987</v>
+        <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701613</v>
+        <v>701675</v>
       </c>
       <c r="R25" t="n">
-        <v>6359973</v>
+        <v>6359988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3340,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,49 +3355,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291987</t>
+          <t>https://artportalen.se/Sighting/137287620</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137268891</v>
+        <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>90919</v>
+        <v>87546</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2072</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,13 +3407,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701433</v>
+        <v>701613</v>
       </c>
       <c r="R26" t="n">
-        <v>6359940</v>
+        <v>6359973</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,22 +3437,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,27 +3467,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268891</t>
+          <t>https://artportalen.se/Sighting/137291987</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137268899</v>
+        <v>137268891</v>
       </c>
       <c r="B27" t="n">
-        <v>90919</v>
+        <v>90920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,10 +3519,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701634</v>
+        <v>701433</v>
       </c>
       <c r="R27" t="n">
-        <v>6360121</v>
+        <v>6359940</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3560,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,54 +3590,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268899</t>
+          <t>https://artportalen.se/Sighting/137268891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308317</v>
+        <v>137268899</v>
       </c>
       <c r="B28" t="n">
-        <v>96708</v>
+        <v>90920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>2072</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701518</v>
+        <v>701634</v>
       </c>
       <c r="R28" t="n">
-        <v>6360129</v>
+        <v>6360121</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3667,12 +3661,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,27 +3691,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308317</t>
+          <t>https://artportalen.se/Sighting/137268899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97356366</v>
+        <v>120308317</v>
       </c>
       <c r="B29" t="n">
-        <v>91680</v>
+        <v>96708</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,37 +3719,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701611</v>
+        <v>701518</v>
       </c>
       <c r="R29" t="n">
-        <v>6359962</v>
+        <v>6360129</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3772,12 +3773,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,34 +3787,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356366</t>
+          <t>https://artportalen.se/Sighting/120308317</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137270003</v>
+        <v>97356366</v>
       </c>
       <c r="B30" t="n">
-        <v>91934</v>
+        <v>91680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,19 +3839,22 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701505</v>
+        <v>701611</v>
       </c>
       <c r="R30" t="n">
-        <v>6359979</v>
+        <v>6359962</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3875,22 +3878,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3899,33 +3892,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270003</t>
+          <t>https://artportalen.se/Sighting/97356366</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69178539</v>
+        <v>137270003</v>
       </c>
       <c r="B31" t="n">
-        <v>87309</v>
+        <v>91935</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3933,46 +3927,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701531</v>
+        <v>701505</v>
       </c>
       <c r="R31" t="n">
-        <v>6360078</v>
+        <v>6359979</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,12 +3981,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,27 +4011,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178539</t>
+          <t>https://artportalen.se/Sighting/137270003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137291990</v>
+        <v>69178539</v>
       </c>
       <c r="B32" t="n">
-        <v>87532</v>
+        <v>87309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,20 +4056,29 @@
           <t>Britzelm.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701724</v>
+        <v>701531</v>
       </c>
       <c r="R32" t="n">
-        <v>6359981</v>
+        <v>6360078</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4098,22 +4102,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,74 +4122,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291990</t>
+          <t>https://artportalen.se/Sighting/69178539</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>69178537</v>
+        <v>137291990</v>
       </c>
       <c r="B33" t="n">
-        <v>87170</v>
+        <v>87533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701531</v>
+        <v>701724</v>
       </c>
       <c r="R33" t="n">
-        <v>6360078</v>
+        <v>6359981</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4219,12 +4204,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,27 +4234,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178537</t>
+          <t>https://artportalen.se/Sighting/137291990</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137268897</v>
+        <v>69178537</v>
       </c>
       <c r="B34" t="n">
-        <v>87393</v>
+        <v>87170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4284,20 +4279,29 @@
           <t>Fr.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701511</v>
+        <v>701531</v>
       </c>
       <c r="R34" t="n">
-        <v>6360175</v>
+        <v>6360078</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4321,22 +4325,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,74 +4345,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268897</t>
+          <t>https://artportalen.se/Sighting/69178537</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>69178534</v>
+        <v>137268897</v>
       </c>
       <c r="B35" t="n">
-        <v>91322</v>
+        <v>87394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701531</v>
+        <v>701511</v>
       </c>
       <c r="R35" t="n">
-        <v>6360078</v>
+        <v>6360175</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,12 +4427,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4462,24 +4457,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178534</t>
+          <t>https://artportalen.se/Sighting/137268897</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89807741</v>
+        <v>69178534</v>
       </c>
       <c r="B36" t="n">
         <v>91322</v>
@@ -4517,21 +4512,19 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701576</v>
+        <v>701531</v>
       </c>
       <c r="R36" t="n">
-        <v>6359964</v>
+        <v>6360078</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4555,12 +4548,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,31 +4562,30 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807741</t>
+          <t>https://artportalen.se/Sighting/69178534</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89807794</v>
+        <v>89807741</v>
       </c>
       <c r="B37" t="n">
         <v>91322</v>
@@ -4623,12 +4615,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4639,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701579</v>
+        <v>701576</v>
       </c>
       <c r="R37" t="n">
-        <v>6359965</v>
+        <v>6359964</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4701,16 +4693,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807794</t>
+          <t>https://artportalen.se/Sighting/89807741</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137271107</v>
+        <v>89807794</v>
       </c>
       <c r="B38" t="n">
-        <v>91552</v>
+        <v>91322</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,17 +4727,28 @@
           <t>Fr.:Pers.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701547</v>
+        <v>701579</v>
       </c>
       <c r="R38" t="n">
-        <v>6359958</v>
+        <v>6359965</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,22 +4775,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,33 +4789,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271107</t>
+          <t>https://artportalen.se/Sighting/89807794</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137271121</v>
+        <v>137271107</v>
       </c>
       <c r="B39" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4854,13 +4848,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701640</v>
+        <v>701547</v>
       </c>
       <c r="R39" t="n">
-        <v>6359976</v>
+        <v>6359958</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4889,7 +4883,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4899,7 +4893,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4925,16 +4919,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271121</t>
+          <t>https://artportalen.se/Sighting/137271107</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137271127</v>
+        <v>137271121</v>
       </c>
       <c r="B40" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4966,10 +4960,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701707</v>
+        <v>701640</v>
       </c>
       <c r="R40" t="n">
-        <v>6359989</v>
+        <v>6359976</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
@@ -5001,7 +4995,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5011,7 +5005,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5037,16 +5031,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271127</t>
+          <t>https://artportalen.se/Sighting/137271121</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137273099</v>
+        <v>137271127</v>
       </c>
       <c r="B41" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5074,17 +5068,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701579</v>
+        <v>701707</v>
       </c>
       <c r="R41" t="n">
-        <v>6359978</v>
+        <v>6359989</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5113,7 +5107,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5123,7 +5117,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5138,27 +5132,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273099</t>
+          <t>https://artportalen.se/Sighting/137271127</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137273105</v>
+        <v>137273099</v>
       </c>
       <c r="B42" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5190,10 +5184,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701705</v>
+        <v>701579</v>
       </c>
       <c r="R42" t="n">
-        <v>6359976</v>
+        <v>6359978</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5225,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5235,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5261,16 +5255,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273105</t>
+          <t>https://artportalen.se/Sighting/137273099</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137291988</v>
+        <v>137273105</v>
       </c>
       <c r="B43" t="n">
-        <v>89312</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5278,34 +5272,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4379</v>
+        <v>4188</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701698</v>
+        <v>701705</v>
       </c>
       <c r="R43" t="n">
-        <v>6359959</v>
+        <v>6359976</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5332,22 +5326,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,27 +5356,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291988</t>
+          <t>https://artportalen.se/Sighting/137273105</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>69178532</v>
+        <v>137291988</v>
       </c>
       <c r="B44" t="n">
-        <v>89143</v>
+        <v>89313</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5390,46 +5384,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4405</v>
+        <v>4379</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701531</v>
+        <v>701698</v>
       </c>
       <c r="R44" t="n">
-        <v>6360078</v>
+        <v>6359959</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5453,12 +5438,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5473,27 +5468,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178532</t>
+          <t>https://artportalen.se/Sighting/137291988</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>89807817</v>
+        <v>69178532</v>
       </c>
       <c r="B45" t="n">
-        <v>92567</v>
+        <v>89143</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5501,21 +5496,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6031</v>
+        <v>4405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5525,24 +5520,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701486</v>
+        <v>701531</v>
       </c>
       <c r="R45" t="n">
-        <v>6359900</v>
+        <v>6360078</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,12 +5559,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5580,56 +5573,55 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807817</t>
+          <t>https://artportalen.se/Sighting/69178532</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>13185284</v>
+        <v>89807817</v>
       </c>
       <c r="B46" t="n">
-        <v>43467</v>
+        <v>92567</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101242</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5637,24 +5629,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701342</v>
+        <v>701486</v>
       </c>
       <c r="R46" t="n">
-        <v>6360057</v>
+        <v>6359900</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5673,17 +5667,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2006-06-30</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2006-06-30</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5692,30 +5686,31 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13185284</t>
+          <t>https://artportalen.se/Sighting/89807817</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>68588838</v>
+        <v>13185284</v>
       </c>
       <c r="B47" t="n">
         <v>43467</v>
@@ -5745,12 +5740,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5758,22 +5748,19 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701415</v>
+        <v>701342</v>
       </c>
       <c r="R47" t="n">
-        <v>6359952</v>
+        <v>6360057</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5797,12 +5784,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,28 +5804,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588838</t>
+          <t>https://artportalen.se/Sighting/13185284</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68588850</v>
+        <v>68588838</v>
       </c>
       <c r="B48" t="n">
         <v>43467</v>
@@ -5868,7 +5851,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5890,10 +5873,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>701382</v>
+        <v>701415</v>
       </c>
       <c r="R48" t="n">
-        <v>6360003</v>
+        <v>6359952</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5955,13 +5938,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588850</t>
+          <t>https://artportalen.se/Sighting/68588838</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68588873</v>
+        <v>68588850</v>
       </c>
       <c r="B49" t="n">
         <v>43467</v>
@@ -5991,7 +5974,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6013,10 +5996,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>701378</v>
+        <v>701382</v>
       </c>
       <c r="R49" t="n">
-        <v>6360008</v>
+        <v>6360003</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6078,13 +6061,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588873</t>
+          <t>https://artportalen.se/Sighting/68588850</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73899486</v>
+        <v>68588873</v>
       </c>
       <c r="B50" t="n">
         <v>43467</v>
@@ -6114,7 +6097,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6136,10 +6119,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>701392</v>
+        <v>701378</v>
       </c>
       <c r="R50" t="n">
-        <v>6359989</v>
+        <v>6360008</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6166,12 +6149,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6180,7 +6163,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6202,13 +6184,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899486</t>
+          <t>https://artportalen.se/Sighting/68588873</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73899493</v>
+        <v>73899486</v>
       </c>
       <c r="B51" t="n">
         <v>43467</v>
@@ -6238,7 +6220,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6260,10 +6242,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>701372</v>
+        <v>701392</v>
       </c>
       <c r="R51" t="n">
-        <v>6360022</v>
+        <v>6359989</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6326,13 +6308,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899493</t>
+          <t>https://artportalen.se/Sighting/73899486</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73899494</v>
+        <v>73899493</v>
       </c>
       <c r="B52" t="n">
         <v>43467</v>
@@ -6384,10 +6366,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>701365</v>
+        <v>701372</v>
       </c>
       <c r="R52" t="n">
-        <v>6360025</v>
+        <v>6360022</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6450,13 +6432,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899494</t>
+          <t>https://artportalen.se/Sighting/73899493</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73899497</v>
+        <v>73899494</v>
       </c>
       <c r="B53" t="n">
         <v>43467</v>
@@ -6486,7 +6468,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6508,10 +6490,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701336</v>
+        <v>701365</v>
       </c>
       <c r="R53" t="n">
-        <v>6360054</v>
+        <v>6360025</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6574,13 +6556,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899497</t>
+          <t>https://artportalen.se/Sighting/73899494</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>80433370</v>
+        <v>73899497</v>
       </c>
       <c r="B54" t="n">
         <v>43467</v>
@@ -6610,7 +6592,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6628,17 +6610,17 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rambasvägen, Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701390</v>
+        <v>701336</v>
       </c>
       <c r="R54" t="n">
-        <v>6360006</v>
+        <v>6360054</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6662,12 +6644,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6698,13 +6680,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80433370</t>
+          <t>https://artportalen.se/Sighting/73899497</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80433374</v>
+        <v>80433370</v>
       </c>
       <c r="B55" t="n">
         <v>43467</v>
@@ -6734,7 +6716,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6756,10 +6738,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701343</v>
+        <v>701390</v>
       </c>
       <c r="R55" t="n">
-        <v>6360056</v>
+        <v>6360006</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6822,13 +6804,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80433374</t>
+          <t>https://artportalen.se/Sighting/80433370</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>88866504</v>
+        <v>80433374</v>
       </c>
       <c r="B56" t="n">
         <v>43467</v>
@@ -6858,10 +6840,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -6872,17 +6858,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701368</v>
+        <v>701343</v>
       </c>
       <c r="R56" t="n">
-        <v>6360019</v>
+        <v>6360056</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6906,12 +6892,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6942,13 +6928,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88866504</t>
+          <t>https://artportalen.se/Sighting/80433374</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>95822713</v>
+        <v>88866504</v>
       </c>
       <c r="B57" t="n">
         <v>43467</v>
@@ -6978,7 +6964,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -6996,10 +6982,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701325</v>
+        <v>701368</v>
       </c>
       <c r="R57" t="n">
-        <v>6360075</v>
+        <v>6360019</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7026,12 +7012,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7062,13 +7048,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95822713</t>
+          <t>https://artportalen.se/Sighting/88866504</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111836843</v>
+        <v>95822713</v>
       </c>
       <c r="B58" t="n">
         <v>43467</v>
@@ -7098,7 +7084,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -7116,13 +7102,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701392</v>
+        <v>701325</v>
       </c>
       <c r="R58" t="n">
-        <v>6359993</v>
+        <v>6360075</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7146,12 +7132,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7182,13 +7168,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111836843</t>
+          <t>https://artportalen.se/Sighting/95822713</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111836851</v>
+        <v>111836843</v>
       </c>
       <c r="B59" t="n">
         <v>43467</v>
@@ -7218,7 +7204,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7236,13 +7222,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701368</v>
+        <v>701392</v>
       </c>
       <c r="R59" t="n">
-        <v>6360029</v>
+        <v>6359993</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7302,13 +7288,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111836851</t>
+          <t>https://artportalen.se/Sighting/111836843</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118077428</v>
+        <v>111836851</v>
       </c>
       <c r="B60" t="n">
         <v>43467</v>
@@ -7338,7 +7324,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7356,10 +7342,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>701334</v>
+        <v>701368</v>
       </c>
       <c r="R60" t="n">
-        <v>6360070</v>
+        <v>6360029</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7386,12 +7372,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7422,13 +7408,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118077428</t>
+          <t>https://artportalen.se/Sighting/111836851</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126992416</v>
+        <v>118077428</v>
       </c>
       <c r="B61" t="n">
         <v>43467</v>
@@ -7476,13 +7462,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>701441</v>
+        <v>701334</v>
       </c>
       <c r="R61" t="n">
-        <v>6359878</v>
+        <v>6360070</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7506,12 +7492,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7542,13 +7528,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992416</t>
+          <t>https://artportalen.se/Sighting/118077428</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126992433</v>
+        <v>126992416</v>
       </c>
       <c r="B62" t="n">
         <v>43467</v>
@@ -7596,10 +7582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701364</v>
+        <v>701441</v>
       </c>
       <c r="R62" t="n">
-        <v>6360029</v>
+        <v>6359878</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7662,13 +7648,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992433</t>
+          <t>https://artportalen.se/Sighting/126992416</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126992447</v>
+        <v>126992433</v>
       </c>
       <c r="B63" t="n">
         <v>43467</v>
@@ -7716,10 +7702,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>701335</v>
+        <v>701364</v>
       </c>
       <c r="R63" t="n">
-        <v>6360059</v>
+        <v>6360029</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7782,38 +7768,38 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992447</t>
+          <t>https://artportalen.se/Sighting/126992433</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129317243</v>
+        <v>126992447</v>
       </c>
       <c r="B64" t="n">
-        <v>43299</v>
+        <v>43467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101260</v>
+        <v>101242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7821,34 +7807,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701618</v>
+        <v>701335</v>
       </c>
       <c r="R64" t="n">
-        <v>6359923</v>
+        <v>6360059</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7867,17 +7847,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7886,70 +7866,80 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Grustag med rikt av backtimjan.</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317243</t>
+          <t>https://artportalen.se/Sighting/126992447</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120308094</v>
+        <v>129317243</v>
       </c>
       <c r="B65" t="n">
-        <v>99093</v>
+        <v>43299</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219797</v>
+        <v>101260</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7958,10 +7948,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>701557</v>
+        <v>701618</v>
       </c>
       <c r="R65" t="n">
-        <v>6360196</v>
+        <v>6359923</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7988,12 +7978,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8007,7 +7997,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Grustag med rikt av backtimjan.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8018,22 +8008,22 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308094</t>
+          <t>https://artportalen.se/Sighting/129317243</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137291989</v>
+        <v>120308094</v>
       </c>
       <c r="B66" t="n">
-        <v>99427</v>
+        <v>99093</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8041,34 +8031,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219862</v>
+        <v>219797</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701700</v>
+        <v>701557</v>
       </c>
       <c r="R66" t="n">
-        <v>6359961</v>
+        <v>6360196</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8095,22 +8094,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8121,66 +8110,71 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291989</t>
+          <t>https://artportalen.se/Sighting/120308094</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120308078</v>
+        <v>137291989</v>
       </c>
       <c r="B67" t="n">
-        <v>104640</v>
+        <v>99428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701622</v>
+        <v>701700</v>
       </c>
       <c r="R67" t="n">
-        <v>6360225</v>
+        <v>6359961</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8207,12 +8201,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8223,33 +8227,28 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308078</t>
+          <t>https://artportalen.se/Sighting/137291989</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120308121</v>
+        <v>120308078</v>
       </c>
       <c r="B68" t="n">
         <v>104640</v>
@@ -8284,13 +8283,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>701398</v>
+        <v>701622</v>
       </c>
       <c r="R68" t="n">
-        <v>6360004</v>
+        <v>6360225</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8333,7 +8332,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mot körvägkant..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8350,16 +8349,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308121</t>
+          <t>https://artportalen.se/Sighting/120308078</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120308124</v>
+        <v>120308121</v>
       </c>
       <c r="B69" t="n">
-        <v>109815</v>
+        <v>104640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8367,33 +8366,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220204</v>
+        <v>220164</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
@@ -8466,16 +8456,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308124</t>
+          <t>https://artportalen.se/Sighting/120308121</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120308042</v>
+        <v>120308124</v>
       </c>
       <c r="B70" t="n">
-        <v>110078</v>
+        <v>109815</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8483,16 +8473,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8500,20 +8490,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701451</v>
+        <v>701398</v>
       </c>
       <c r="R70" t="n">
-        <v>6359994</v>
+        <v>6360004</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8556,7 +8555,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8573,13 +8572,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308042</t>
+          <t>https://artportalen.se/Sighting/120308124</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120308086</v>
+        <v>120308042</v>
       </c>
       <c r="B71" t="n">
         <v>110078</v>
@@ -8614,13 +8613,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>701557</v>
+        <v>701451</v>
       </c>
       <c r="R71" t="n">
-        <v>6360196</v>
+        <v>6359994</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8663,7 +8662,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8680,13 +8679,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308086</t>
+          <t>https://artportalen.se/Sighting/120308042</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120308105</v>
+        <v>120308086</v>
       </c>
       <c r="B72" t="n">
         <v>110078</v>
@@ -8714,29 +8713,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>701480</v>
+        <v>701557</v>
       </c>
       <c r="R72" t="n">
-        <v>6360120</v>
+        <v>6360196</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8796,16 +8786,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308105</t>
+          <t>https://artportalen.se/Sighting/120308086</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120308043</v>
+        <v>120308105</v>
       </c>
       <c r="B73" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8813,16 +8803,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8830,20 +8820,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>701451</v>
+        <v>701480</v>
       </c>
       <c r="R73" t="n">
-        <v>6359994</v>
+        <v>6360120</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8886,7 +8885,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8903,13 +8902,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308043</t>
+          <t>https://artportalen.se/Sighting/120308105</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120308052</v>
+        <v>120308043</v>
       </c>
       <c r="B74" t="n">
         <v>107517</v>
@@ -8944,10 +8943,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701467</v>
+        <v>701451</v>
       </c>
       <c r="R74" t="n">
-        <v>6359951</v>
+        <v>6359994</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9010,13 +9009,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308052</t>
+          <t>https://artportalen.se/Sighting/120308043</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120308053</v>
+        <v>120308052</v>
       </c>
       <c r="B75" t="n">
         <v>107517</v>
@@ -9051,10 +9050,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701497</v>
+        <v>701467</v>
       </c>
       <c r="R75" t="n">
-        <v>6359955</v>
+        <v>6359951</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9117,13 +9116,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308053</t>
+          <t>https://artportalen.se/Sighting/120308052</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120308055</v>
+        <v>120308053</v>
       </c>
       <c r="B76" t="n">
         <v>107517</v>
@@ -9158,10 +9157,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>701519</v>
+        <v>701497</v>
       </c>
       <c r="R76" t="n">
-        <v>6359965</v>
+        <v>6359955</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9224,13 +9223,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308055</t>
+          <t>https://artportalen.se/Sighting/120308053</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120308059</v>
+        <v>120308055</v>
       </c>
       <c r="B77" t="n">
         <v>107517</v>
@@ -9265,10 +9264,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>701524</v>
+        <v>701519</v>
       </c>
       <c r="R77" t="n">
-        <v>6359992</v>
+        <v>6359965</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9314,7 +9313,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9331,13 +9330,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308059</t>
+          <t>https://artportalen.se/Sighting/120308055</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120308060</v>
+        <v>120308059</v>
       </c>
       <c r="B78" t="n">
         <v>107517</v>
@@ -9372,10 +9371,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701526</v>
+        <v>701524</v>
       </c>
       <c r="R78" t="n">
-        <v>6360046</v>
+        <v>6359992</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9421,7 +9420,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9438,13 +9437,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308060</t>
+          <t>https://artportalen.se/Sighting/120308059</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120308062</v>
+        <v>120308060</v>
       </c>
       <c r="B79" t="n">
         <v>107517</v>
@@ -9479,10 +9478,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701524</v>
+        <v>701526</v>
       </c>
       <c r="R79" t="n">
-        <v>6360079</v>
+        <v>6360046</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9545,13 +9544,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308062</t>
+          <t>https://artportalen.se/Sighting/120308060</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120308063</v>
+        <v>120308062</v>
       </c>
       <c r="B80" t="n">
         <v>107517</v>
@@ -9586,10 +9585,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>701532</v>
+        <v>701524</v>
       </c>
       <c r="R80" t="n">
-        <v>6360141</v>
+        <v>6360079</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9652,13 +9651,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308063</t>
+          <t>https://artportalen.se/Sighting/120308062</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120308066</v>
+        <v>120308063</v>
       </c>
       <c r="B81" t="n">
         <v>107517</v>
@@ -9693,10 +9692,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701560</v>
+        <v>701532</v>
       </c>
       <c r="R81" t="n">
-        <v>6360140</v>
+        <v>6360141</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9731,11 +9730,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9747,7 +9741,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9764,13 +9758,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308066</t>
+          <t>https://artportalen.se/Sighting/120308063</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120308067</v>
+        <v>120308066</v>
       </c>
       <c r="B82" t="n">
         <v>107517</v>
@@ -9805,7 +9799,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701574</v>
+        <v>701560</v>
       </c>
       <c r="R82" t="n">
         <v>6360140</v>
@@ -9843,6 +9837,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9871,13 +9870,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308067</t>
+          <t>https://artportalen.se/Sighting/120308066</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120308068</v>
+        <v>120308067</v>
       </c>
       <c r="B83" t="n">
         <v>107517</v>
@@ -9912,13 +9911,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>701594</v>
+        <v>701574</v>
       </c>
       <c r="R83" t="n">
-        <v>6360147</v>
+        <v>6360140</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9978,13 +9977,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308068</t>
+          <t>https://artportalen.se/Sighting/120308067</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120308071</v>
+        <v>120308068</v>
       </c>
       <c r="B84" t="n">
         <v>107517</v>
@@ -10019,13 +10018,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701636</v>
+        <v>701594</v>
       </c>
       <c r="R84" t="n">
-        <v>6360182</v>
+        <v>6360147</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10085,13 +10084,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308071</t>
+          <t>https://artportalen.se/Sighting/120308068</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120308076</v>
+        <v>120308071</v>
       </c>
       <c r="B85" t="n">
         <v>107517</v>
@@ -10126,10 +10125,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701638</v>
+        <v>701636</v>
       </c>
       <c r="R85" t="n">
-        <v>6360226</v>
+        <v>6360182</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10151,7 +10150,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -10175,7 +10174,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta i gränsgata.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10192,13 +10191,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308076</t>
+          <t>https://artportalen.se/Sighting/120308071</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120308080</v>
+        <v>120308076</v>
       </c>
       <c r="B86" t="n">
         <v>107517</v>
@@ -10233,10 +10232,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701606</v>
+        <v>701638</v>
       </c>
       <c r="R86" t="n">
-        <v>6360224</v>
+        <v>6360226</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10258,7 +10257,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10282,7 +10281,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10299,13 +10298,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308080</t>
+          <t>https://artportalen.se/Sighting/120308076</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120308092</v>
+        <v>120308080</v>
       </c>
       <c r="B87" t="n">
         <v>107517</v>
@@ -10340,10 +10339,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701557</v>
+        <v>701606</v>
       </c>
       <c r="R87" t="n">
-        <v>6360196</v>
+        <v>6360224</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10389,7 +10388,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10406,13 +10405,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308092</t>
+          <t>https://artportalen.se/Sighting/120308080</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120308100</v>
+        <v>120308092</v>
       </c>
       <c r="B88" t="n">
         <v>107517</v>
@@ -10447,13 +10446,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701541</v>
+        <v>701557</v>
       </c>
       <c r="R88" t="n">
-        <v>6360151</v>
+        <v>6360196</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10513,13 +10512,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308100</t>
+          <t>https://artportalen.se/Sighting/120308092</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120308102</v>
+        <v>120308100</v>
       </c>
       <c r="B89" t="n">
         <v>107517</v>
@@ -10554,13 +10553,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>701532</v>
+        <v>701541</v>
       </c>
       <c r="R89" t="n">
-        <v>6360143</v>
+        <v>6360151</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10620,13 +10619,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308102</t>
+          <t>https://artportalen.se/Sighting/120308100</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120308106</v>
+        <v>120308102</v>
       </c>
       <c r="B90" t="n">
         <v>107517</v>
@@ -10661,13 +10660,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>701480</v>
+        <v>701532</v>
       </c>
       <c r="R90" t="n">
-        <v>6360120</v>
+        <v>6360143</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10727,13 +10726,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308106</t>
+          <t>https://artportalen.se/Sighting/120308102</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120308107</v>
+        <v>120308106</v>
       </c>
       <c r="B91" t="n">
         <v>107517</v>
@@ -10768,10 +10767,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>701452</v>
+        <v>701480</v>
       </c>
       <c r="R91" t="n">
-        <v>6360109</v>
+        <v>6360120</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10834,13 +10833,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308107</t>
+          <t>https://artportalen.se/Sighting/120308106</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120308109</v>
+        <v>120308107</v>
       </c>
       <c r="B92" t="n">
         <v>107517</v>
@@ -10875,10 +10874,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>701431</v>
+        <v>701452</v>
       </c>
       <c r="R92" t="n">
-        <v>6360091</v>
+        <v>6360109</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10941,13 +10940,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308109</t>
+          <t>https://artportalen.se/Sighting/120308107</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120308110</v>
+        <v>120308109</v>
       </c>
       <c r="B93" t="n">
         <v>107517</v>
@@ -10982,10 +10981,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>701423</v>
+        <v>701431</v>
       </c>
       <c r="R93" t="n">
-        <v>6360088</v>
+        <v>6360091</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11048,13 +11047,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308110</t>
+          <t>https://artportalen.se/Sighting/120308109</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120308112</v>
+        <v>120308110</v>
       </c>
       <c r="B94" t="n">
         <v>107517</v>
@@ -11089,13 +11088,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>701407</v>
+        <v>701423</v>
       </c>
       <c r="R94" t="n">
-        <v>6360080</v>
+        <v>6360088</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11155,13 +11154,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308112</t>
+          <t>https://artportalen.se/Sighting/120308110</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120308122</v>
+        <v>120308112</v>
       </c>
       <c r="B95" t="n">
         <v>107517</v>
@@ -11196,13 +11195,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>701398</v>
+        <v>701407</v>
       </c>
       <c r="R95" t="n">
-        <v>6360004</v>
+        <v>6360080</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11245,7 +11244,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mot körvägkant..</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11262,16 +11261,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308122</t>
+          <t>https://artportalen.se/Sighting/120308112</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129317272</v>
+        <v>120308122</v>
       </c>
       <c r="B96" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11303,13 +11302,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>701618</v>
+        <v>701398</v>
       </c>
       <c r="R96" t="n">
-        <v>6359923</v>
+        <v>6360004</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11333,12 +11332,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11352,7 +11351,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Grustag.</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11363,68 +11362,57 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317272</t>
+          <t>https://artportalen.se/Sighting/120308122</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>89823813</v>
+        <v>129317272</v>
       </c>
       <c r="B97" t="n">
-        <v>87291</v>
+        <v>107516</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>248955</v>
+        <v>221849</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>701391</v>
+        <v>701618</v>
       </c>
       <c r="R97" t="n">
-        <v>6359996</v>
+        <v>6359923</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11446,17 +11434,17 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11465,34 +11453,38 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Grustag.</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89823813</t>
+          <t>https://artportalen.se/Sighting/129317272</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137268893</v>
+        <v>89823813</v>
       </c>
       <c r="B98" t="n">
-        <v>87485</v>
+        <v>87291</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11500,34 +11492,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>701437</v>
+        <v>701391</v>
       </c>
       <c r="R98" t="n">
-        <v>6359977</v>
+        <v>6359996</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11549,27 +11552,17 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-11-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-11-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11578,33 +11571,34 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268893</t>
+          <t>https://artportalen.se/Sighting/89823813</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137268896</v>
+        <v>137268893</v>
       </c>
       <c r="B99" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11636,10 +11630,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>701505</v>
+        <v>701437</v>
       </c>
       <c r="R99" t="n">
-        <v>6360156</v>
+        <v>6359977</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11671,7 +11665,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11681,7 +11675,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11707,16 +11701,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268896</t>
+          <t>https://artportalen.se/Sighting/137268893</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137268902</v>
+        <v>137268896</v>
       </c>
       <c r="B100" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11748,10 +11742,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>701632</v>
+        <v>701505</v>
       </c>
       <c r="R100" t="n">
-        <v>6360096</v>
+        <v>6360156</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11783,7 +11777,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11793,7 +11787,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11819,16 +11813,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268902</t>
+          <t>https://artportalen.se/Sighting/137268896</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137270002</v>
+        <v>137268902</v>
       </c>
       <c r="B101" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11856,17 +11850,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>701481</v>
+        <v>701632</v>
       </c>
       <c r="R101" t="n">
-        <v>6359978</v>
+        <v>6360096</v>
       </c>
       <c r="S101" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11895,7 +11889,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11905,7 +11899,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11920,27 +11914,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270002</t>
+          <t>https://artportalen.se/Sighting/137268902</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137271098</v>
+        <v>137270002</v>
       </c>
       <c r="B102" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11968,17 +11962,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>701484</v>
+        <v>701481</v>
       </c>
       <c r="R102" t="n">
-        <v>6359923</v>
+        <v>6359978</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12007,7 +12001,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12017,7 +12011,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12032,27 +12026,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271098</t>
+          <t>https://artportalen.se/Sighting/137270002</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137271110</v>
+        <v>137271098</v>
       </c>
       <c r="B103" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12084,10 +12078,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>701553</v>
+        <v>701484</v>
       </c>
       <c r="R103" t="n">
-        <v>6359994</v>
+        <v>6359923</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12119,7 +12113,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12129,7 +12123,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12155,16 +12149,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271110</t>
+          <t>https://artportalen.se/Sighting/137271098</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137271118</v>
+        <v>137271110</v>
       </c>
       <c r="B104" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12196,13 +12190,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>701619</v>
+        <v>701553</v>
       </c>
       <c r="R104" t="n">
-        <v>6359978</v>
+        <v>6359994</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12231,7 +12225,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12241,7 +12235,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12267,16 +12261,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271118</t>
+          <t>https://artportalen.se/Sighting/137271110</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137273092</v>
+        <v>137271118</v>
       </c>
       <c r="B105" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12304,17 +12298,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701412</v>
+        <v>701619</v>
       </c>
       <c r="R105" t="n">
-        <v>6360078</v>
+        <v>6359978</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12343,7 +12337,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12353,7 +12347,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12368,27 +12362,27 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273092</t>
+          <t>https://artportalen.se/Sighting/137271118</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137273103</v>
+        <v>137273092</v>
       </c>
       <c r="B106" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12420,10 +12414,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701648</v>
+        <v>701412</v>
       </c>
       <c r="R106" t="n">
-        <v>6360005</v>
+        <v>6360078</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12455,7 +12449,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12465,7 +12459,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12491,16 +12485,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273103</t>
+          <t>https://artportalen.se/Sighting/137273092</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137313530</v>
+        <v>137273103</v>
       </c>
       <c r="B107" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12532,13 +12526,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701645</v>
+        <v>701648</v>
       </c>
       <c r="R107" t="n">
-        <v>6359988</v>
+        <v>6360005</v>
       </c>
       <c r="S107" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12562,22 +12556,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12592,74 +12586,65 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313530</t>
+          <t>https://artportalen.se/Sighting/137273103</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>69178541</v>
+        <v>137313530</v>
       </c>
       <c r="B108" t="n">
-        <v>87346</v>
+        <v>87486</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701531</v>
+        <v>701645</v>
       </c>
       <c r="R108" t="n">
-        <v>6360078</v>
+        <v>6359988</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12683,12 +12668,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12703,24 +12698,24 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178541</t>
+          <t>https://artportalen.se/Sighting/137313530</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>89804386</v>
+        <v>69178541</v>
       </c>
       <c r="B109" t="n">
         <v>87346</v>
@@ -12758,21 +12753,19 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701357</v>
+        <v>701531</v>
       </c>
       <c r="R109" t="n">
-        <v>6360028</v>
+        <v>6360078</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12791,17 +12784,17 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12810,34 +12803,33 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89804386</t>
+          <t>https://artportalen.se/Sighting/69178541</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137268901</v>
+        <v>89804386</v>
       </c>
       <c r="B110" t="n">
-        <v>87569</v>
+        <v>87346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12862,17 +12854,28 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701648</v>
+        <v>701357</v>
       </c>
       <c r="R110" t="n">
-        <v>6360091</v>
+        <v>6360028</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12894,27 +12897,17 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12930,27 +12923,27 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268901</t>
+          <t>https://artportalen.se/Sighting/89804386</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137271099</v>
+        <v>137268901</v>
       </c>
       <c r="B111" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12978,17 +12971,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>701497</v>
+        <v>701648</v>
       </c>
       <c r="R111" t="n">
-        <v>6359942</v>
+        <v>6360091</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13017,7 +13010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13027,7 +13020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13036,33 +13029,34 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271099</t>
+          <t>https://artportalen.se/Sighting/137268901</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137271101</v>
+        <v>137271099</v>
       </c>
       <c r="B112" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13094,10 +13088,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701511</v>
+        <v>701497</v>
       </c>
       <c r="R112" t="n">
-        <v>6359954</v>
+        <v>6359942</v>
       </c>
       <c r="S112" t="n">
         <v>7</v>
@@ -13129,7 +13123,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13139,7 +13133,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13165,16 +13159,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271101</t>
+          <t>https://artportalen.se/Sighting/137271099</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137271102</v>
+        <v>137271101</v>
       </c>
       <c r="B113" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13206,13 +13200,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701503</v>
+        <v>701511</v>
       </c>
       <c r="R113" t="n">
-        <v>6359960</v>
+        <v>6359954</v>
       </c>
       <c r="S113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13241,7 +13235,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13251,7 +13245,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13277,16 +13271,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271102</t>
+          <t>https://artportalen.se/Sighting/137271101</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137271104</v>
+        <v>137271102</v>
       </c>
       <c r="B114" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13318,13 +13312,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>701539</v>
+        <v>701503</v>
       </c>
       <c r="R114" t="n">
-        <v>6359971</v>
+        <v>6359960</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13353,7 +13347,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13363,7 +13357,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13389,16 +13383,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271104</t>
+          <t>https://artportalen.se/Sighting/137271102</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137271105</v>
+        <v>137271104</v>
       </c>
       <c r="B115" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13430,13 +13424,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>701536</v>
+        <v>701539</v>
       </c>
       <c r="R115" t="n">
-        <v>6359951</v>
+        <v>6359971</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13465,7 +13459,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13475,7 +13469,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13501,16 +13495,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271105</t>
+          <t>https://artportalen.se/Sighting/137271104</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137271111</v>
+        <v>137271105</v>
       </c>
       <c r="B116" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13542,13 +13536,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>701561</v>
+        <v>701536</v>
       </c>
       <c r="R116" t="n">
-        <v>6360029</v>
+        <v>6359951</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13571,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13587,7 +13581,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13613,16 +13607,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271111</t>
+          <t>https://artportalen.se/Sighting/137271105</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137271114</v>
+        <v>137271111</v>
       </c>
       <c r="B117" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13654,13 +13648,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>701604</v>
+        <v>701561</v>
       </c>
       <c r="R117" t="n">
-        <v>6360076</v>
+        <v>6360029</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13689,7 +13683,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13699,7 +13693,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13725,16 +13719,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271114</t>
+          <t>https://artportalen.se/Sighting/137271111</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137271120</v>
+        <v>137271114</v>
       </c>
       <c r="B118" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13766,10 +13760,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>701636</v>
+        <v>701604</v>
       </c>
       <c r="R118" t="n">
-        <v>6359977</v>
+        <v>6360076</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13801,7 +13795,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13811,7 +13805,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13837,16 +13831,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271120</t>
+          <t>https://artportalen.se/Sighting/137271114</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137271123</v>
+        <v>137271120</v>
       </c>
       <c r="B119" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13878,10 +13872,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701680</v>
+        <v>701636</v>
       </c>
       <c r="R119" t="n">
-        <v>6359996</v>
+        <v>6359977</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13913,7 +13907,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13923,7 +13917,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13949,16 +13943,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271123</t>
+          <t>https://artportalen.se/Sighting/137271120</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137271125</v>
+        <v>137271123</v>
       </c>
       <c r="B120" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13990,10 +13984,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701684</v>
+        <v>701680</v>
       </c>
       <c r="R120" t="n">
-        <v>6359985</v>
+        <v>6359996</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14025,7 +14019,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14035,7 +14029,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14061,16 +14055,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271125</t>
+          <t>https://artportalen.se/Sighting/137271123</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137273090</v>
+        <v>137271125</v>
       </c>
       <c r="B121" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14098,14 +14092,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701447</v>
+        <v>701684</v>
       </c>
       <c r="R121" t="n">
-        <v>6359950</v>
+        <v>6359985</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14137,7 +14131,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14147,7 +14141,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14156,34 +14150,33 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273090</t>
+          <t>https://artportalen.se/Sighting/137271125</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137273096</v>
+        <v>137273090</v>
       </c>
       <c r="B122" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14215,10 +14208,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701577</v>
+        <v>701447</v>
       </c>
       <c r="R122" t="n">
-        <v>6360063</v>
+        <v>6359950</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14250,7 +14243,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14260,7 +14253,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14287,16 +14280,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273096</t>
+          <t>https://artportalen.se/Sighting/137273090</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137273098</v>
+        <v>137273096</v>
       </c>
       <c r="B123" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14328,10 +14321,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701552</v>
+        <v>701577</v>
       </c>
       <c r="R123" t="n">
-        <v>6360025</v>
+        <v>6360063</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14363,7 +14356,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14373,7 +14366,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14400,16 +14393,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273098</t>
+          <t>https://artportalen.se/Sighting/137273096</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137273100</v>
+        <v>137273098</v>
       </c>
       <c r="B124" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14441,10 +14434,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701602</v>
+        <v>701552</v>
       </c>
       <c r="R124" t="n">
-        <v>6359969</v>
+        <v>6360025</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14476,7 +14469,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14486,7 +14479,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14513,16 +14506,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273100</t>
+          <t>https://artportalen.se/Sighting/137273098</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137273104</v>
+        <v>137273100</v>
       </c>
       <c r="B125" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14554,10 +14547,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701659</v>
+        <v>701602</v>
       </c>
       <c r="R125" t="n">
-        <v>6360008</v>
+        <v>6359969</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14589,7 +14582,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14599,7 +14592,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14626,54 +14619,54 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273104</t>
+          <t>https://artportalen.se/Sighting/137273100</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137271117</v>
+        <v>137273104</v>
       </c>
       <c r="B126" t="n">
-        <v>87597</v>
+        <v>87570</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6052416</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>701617</v>
+        <v>701659</v>
       </c>
       <c r="R126" t="n">
-        <v>6359978</v>
+        <v>6360008</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14702,7 +14695,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14712,7 +14705,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14721,22 +14714,135 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273104</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>137271117</v>
+      </c>
+      <c r="B127" t="n">
+        <v>87598</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>701617</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6359978</v>
+      </c>
+      <c r="S127" t="n">
+        <v>6</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271117</t>
         </is>
@@ -14869,6 +14975,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87368</v>
+        <v>87371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87368</v>
+        <v>87371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137268891</v>
       </c>
       <c r="B27" t="n">
-        <v>90920</v>
+        <v>90923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137268899</v>
       </c>
       <c r="B28" t="n">
-        <v>90920</v>
+        <v>90923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137270003</v>
       </c>
       <c r="B31" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>137291990</v>
       </c>
       <c r="B33" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137268897</v>
       </c>
       <c r="B35" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>137271107</v>
       </c>
       <c r="B39" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>137271121</v>
       </c>
       <c r="B40" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>137271127</v>
       </c>
       <c r="B41" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>137273099</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137273105</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137291988</v>
       </c>
       <c r="B44" t="n">
-        <v>89313</v>
+        <v>89316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>137291989</v>
       </c>
       <c r="B67" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>137268893</v>
       </c>
       <c r="B99" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>137268896</v>
       </c>
       <c r="B100" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>137268902</v>
       </c>
       <c r="B101" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137270002</v>
       </c>
       <c r="B102" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>137271098</v>
       </c>
       <c r="B103" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137271110</v>
       </c>
       <c r="B104" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>137271118</v>
       </c>
       <c r="B105" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>137273092</v>
       </c>
       <c r="B106" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>137273103</v>
       </c>
       <c r="B107" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>137313530</v>
       </c>
       <c r="B108" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>137268901</v>
       </c>
       <c r="B111" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>137271099</v>
       </c>
       <c r="B112" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137271101</v>
       </c>
       <c r="B113" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>137271102</v>
       </c>
       <c r="B114" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>137271104</v>
       </c>
       <c r="B115" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>137271105</v>
       </c>
       <c r="B116" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>137271111</v>
       </c>
       <c r="B117" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>137271114</v>
       </c>
       <c r="B118" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>137271120</v>
       </c>
       <c r="B119" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>137271123</v>
       </c>
       <c r="B120" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>137271125</v>
       </c>
       <c r="B121" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>137273090</v>
       </c>
       <c r="B122" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>137273096</v>
       </c>
       <c r="B123" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>137273098</v>
       </c>
       <c r="B124" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>137273100</v>
       </c>
       <c r="B125" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>137273104</v>
       </c>
       <c r="B126" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>137271117</v>
       </c>
       <c r="B127" t="n">
-        <v>87598</v>
+        <v>87601</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ127"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3919,7 +3919,7 @@
         <v>137270003</v>
       </c>
       <c r="B31" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>137271107</v>
       </c>
       <c r="B39" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>137271121</v>
       </c>
       <c r="B40" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>137271127</v>
       </c>
       <c r="B41" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>137273099</v>
       </c>
       <c r="B42" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137273105</v>
       </c>
       <c r="B43" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>137291989</v>
       </c>
       <c r="B67" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -14738,48 +14738,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>137271117</v>
+        <v>137313528</v>
       </c>
       <c r="B127" t="n">
-        <v>87601</v>
+        <v>87573</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6052416</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>701617</v>
+        <v>701582</v>
       </c>
       <c r="R127" t="n">
-        <v>6359978</v>
+        <v>6359972</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14803,22 +14803,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14827,22 +14827,135 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137313528</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>137271117</v>
+      </c>
+      <c r="B128" t="n">
+        <v>87601</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>701617</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6359978</v>
+      </c>
+      <c r="S128" t="n">
+        <v>6</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271117</t>
         </is>
@@ -14976,6 +15089,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87371</v>
+        <v>87376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87371</v>
+        <v>87376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137268891</v>
       </c>
       <c r="B27" t="n">
-        <v>90923</v>
+        <v>90928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137268899</v>
       </c>
       <c r="B28" t="n">
-        <v>90923</v>
+        <v>90928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137270003</v>
       </c>
       <c r="B31" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>137291990</v>
       </c>
       <c r="B33" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137268897</v>
       </c>
       <c r="B35" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>137271107</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>137271121</v>
       </c>
       <c r="B40" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>137271127</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>137273099</v>
       </c>
       <c r="B42" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137273105</v>
       </c>
       <c r="B43" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137291988</v>
       </c>
       <c r="B44" t="n">
-        <v>89316</v>
+        <v>89321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>137291989</v>
       </c>
       <c r="B67" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>137268893</v>
       </c>
       <c r="B99" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>137268896</v>
       </c>
       <c r="B100" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>137268902</v>
       </c>
       <c r="B101" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137270002</v>
       </c>
       <c r="B102" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>137271098</v>
       </c>
       <c r="B103" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137271110</v>
       </c>
       <c r="B104" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>137271118</v>
       </c>
       <c r="B105" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>137273092</v>
       </c>
       <c r="B106" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>137273103</v>
       </c>
       <c r="B107" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>137313530</v>
       </c>
       <c r="B108" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>137268901</v>
       </c>
       <c r="B111" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>137271099</v>
       </c>
       <c r="B112" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137271101</v>
       </c>
       <c r="B113" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>137271102</v>
       </c>
       <c r="B114" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>137271104</v>
       </c>
       <c r="B115" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>137271105</v>
       </c>
       <c r="B116" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>137271111</v>
       </c>
       <c r="B117" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>137271114</v>
       </c>
       <c r="B118" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>137271120</v>
       </c>
       <c r="B119" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>137271123</v>
       </c>
       <c r="B120" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>137271125</v>
       </c>
       <c r="B121" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>137273090</v>
       </c>
       <c r="B122" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>137273096</v>
       </c>
       <c r="B123" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>137273098</v>
       </c>
       <c r="B124" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>137273100</v>
       </c>
       <c r="B125" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>137273104</v>
       </c>
       <c r="B126" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>137313528</v>
       </c>
       <c r="B127" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>137271117</v>
       </c>
       <c r="B128" t="n">
-        <v>87601</v>
+        <v>87606</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ128"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3484,48 +3484,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137268891</v>
+        <v>137417962</v>
       </c>
       <c r="B27" t="n">
-        <v>90928</v>
+        <v>91950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2072</v>
+        <v>2015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701433</v>
+        <v>701551</v>
       </c>
       <c r="R27" t="n">
-        <v>6359940</v>
+        <v>6360057</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,22 +3552,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3573,30 +3566,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268891</t>
+          <t>https://artportalen.se/Sighting/137417962</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137268899</v>
+        <v>137268891</v>
       </c>
       <c r="B28" t="n">
         <v>90928</v>
@@ -3631,10 +3625,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701634</v>
+        <v>701433</v>
       </c>
       <c r="R28" t="n">
-        <v>6360121</v>
+        <v>6359940</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3666,7 +3660,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,7 +3670,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3702,54 +3696,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268899</t>
+          <t>https://artportalen.se/Sighting/137268891</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308317</v>
+        <v>137268899</v>
       </c>
       <c r="B29" t="n">
-        <v>96708</v>
+        <v>90928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>2072</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701518</v>
+        <v>701634</v>
       </c>
       <c r="R29" t="n">
-        <v>6360129</v>
+        <v>6360121</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3773,12 +3767,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3793,27 +3797,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308317</t>
+          <t>https://artportalen.se/Sighting/137268899</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97356366</v>
+        <v>120308317</v>
       </c>
       <c r="B30" t="n">
-        <v>91680</v>
+        <v>96708</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3821,37 +3825,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701611</v>
+        <v>701518</v>
       </c>
       <c r="R30" t="n">
-        <v>6359962</v>
+        <v>6360129</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,12 +3879,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3892,34 +3893,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356366</t>
+          <t>https://artportalen.se/Sighting/120308317</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137270003</v>
+        <v>97356366</v>
       </c>
       <c r="B31" t="n">
-        <v>91945</v>
+        <v>91680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,19 +3945,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701505</v>
+        <v>701611</v>
       </c>
       <c r="R31" t="n">
-        <v>6359979</v>
+        <v>6359962</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3981,22 +3984,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4005,33 +3998,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270003</t>
+          <t>https://artportalen.se/Sighting/97356366</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>69178539</v>
+        <v>137270003</v>
       </c>
       <c r="B32" t="n">
-        <v>87309</v>
+        <v>91945</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,46 +4033,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701531</v>
+        <v>701505</v>
       </c>
       <c r="R32" t="n">
-        <v>6360078</v>
+        <v>6359979</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4102,12 +4087,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,27 +4117,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178539</t>
+          <t>https://artportalen.se/Sighting/137270003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137291990</v>
+        <v>69178539</v>
       </c>
       <c r="B33" t="n">
-        <v>87541</v>
+        <v>87309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,20 +4162,29 @@
           <t>Britzelm.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701724</v>
+        <v>701531</v>
       </c>
       <c r="R33" t="n">
-        <v>6359981</v>
+        <v>6360078</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,22 +4208,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,74 +4228,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291990</t>
+          <t>https://artportalen.se/Sighting/69178539</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>69178537</v>
+        <v>137291990</v>
       </c>
       <c r="B34" t="n">
-        <v>87170</v>
+        <v>87541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701531</v>
+        <v>701724</v>
       </c>
       <c r="R34" t="n">
-        <v>6360078</v>
+        <v>6359981</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4325,12 +4310,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,65 +4340,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178537</t>
+          <t>https://artportalen.se/Sighting/137291990</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137268897</v>
+        <v>137417983</v>
       </c>
       <c r="B35" t="n">
-        <v>87402</v>
+        <v>87541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701511</v>
+        <v>701644</v>
       </c>
       <c r="R35" t="n">
-        <v>6360175</v>
+        <v>6360087</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4427,22 +4425,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4451,55 +4439,56 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268897</t>
+          <t>https://artportalen.se/Sighting/137417983</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>69178534</v>
+        <v>69178537</v>
       </c>
       <c r="B36" t="n">
-        <v>91322</v>
+        <v>87170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4579,62 +4568,51 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178534</t>
+          <t>https://artportalen.se/Sighting/69178537</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89807741</v>
+        <v>137268897</v>
       </c>
       <c r="B37" t="n">
-        <v>91322</v>
+        <v>87402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701576</v>
+        <v>701511</v>
       </c>
       <c r="R37" t="n">
-        <v>6359964</v>
+        <v>6360175</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,12 +4639,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,31 +4663,30 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807741</t>
+          <t>https://artportalen.se/Sighting/137268897</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89807794</v>
+        <v>69178534</v>
       </c>
       <c r="B38" t="n">
         <v>91322</v>
@@ -4729,29 +4716,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701579</v>
+        <v>701531</v>
       </c>
       <c r="R38" t="n">
-        <v>6359965</v>
+        <v>6360078</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4775,12 +4760,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,34 +4774,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807794</t>
+          <t>https://artportalen.se/Sighting/69178534</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137271107</v>
+        <v>89807741</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>91322</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,17 +4825,28 @@
           <t>Fr.:Pers.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701547</v>
+        <v>701576</v>
       </c>
       <c r="R39" t="n">
-        <v>6359958</v>
+        <v>6359964</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4878,22 +4873,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4902,33 +4887,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271107</t>
+          <t>https://artportalen.se/Sighting/89807741</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137271121</v>
+        <v>89807794</v>
       </c>
       <c r="B40" t="n">
-        <v>91563</v>
+        <v>91322</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4953,20 +4939,31 @@
           <t>Fr.:Pers.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701640</v>
+        <v>701579</v>
       </c>
       <c r="R40" t="n">
-        <v>6359976</v>
+        <v>6359965</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4990,22 +4987,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5014,30 +5001,31 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271121</t>
+          <t>https://artportalen.se/Sighting/89807794</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137271127</v>
+        <v>137271107</v>
       </c>
       <c r="B41" t="n">
         <v>91563</v>
@@ -5072,13 +5060,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701707</v>
+        <v>701547</v>
       </c>
       <c r="R41" t="n">
-        <v>6359989</v>
+        <v>6359958</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5107,7 +5095,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5117,7 +5105,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5143,13 +5131,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271127</t>
+          <t>https://artportalen.se/Sighting/137271107</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137273099</v>
+        <v>137271121</v>
       </c>
       <c r="B42" t="n">
         <v>91563</v>
@@ -5180,17 +5168,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701579</v>
+        <v>701640</v>
       </c>
       <c r="R42" t="n">
-        <v>6359978</v>
+        <v>6359976</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5219,7 +5207,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5229,7 +5217,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5244,24 +5232,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273099</t>
+          <t>https://artportalen.se/Sighting/137271121</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137273105</v>
+        <v>137271127</v>
       </c>
       <c r="B43" t="n">
         <v>91563</v>
@@ -5292,17 +5280,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701705</v>
+        <v>701707</v>
       </c>
       <c r="R43" t="n">
-        <v>6359976</v>
+        <v>6359989</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5331,7 +5319,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5341,7 +5329,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5356,27 +5344,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273105</t>
+          <t>https://artportalen.se/Sighting/137271127</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137291988</v>
+        <v>137273099</v>
       </c>
       <c r="B44" t="n">
-        <v>89321</v>
+        <v>91563</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5384,34 +5372,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4379</v>
+        <v>4188</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701698</v>
+        <v>701579</v>
       </c>
       <c r="R44" t="n">
-        <v>6359959</v>
+        <v>6359978</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5438,22 +5426,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5468,27 +5456,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291988</t>
+          <t>https://artportalen.se/Sighting/137273099</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>69178532</v>
+        <v>137273105</v>
       </c>
       <c r="B45" t="n">
-        <v>89143</v>
+        <v>91563</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5496,46 +5484,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4405</v>
+        <v>4188</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701531</v>
+        <v>701705</v>
       </c>
       <c r="R45" t="n">
-        <v>6360078</v>
+        <v>6359976</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5559,12 +5538,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,27 +5568,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178532</t>
+          <t>https://artportalen.se/Sighting/137273105</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>89807817</v>
+        <v>137291988</v>
       </c>
       <c r="B46" t="n">
-        <v>92567</v>
+        <v>89321</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5607,45 +5596,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>4379</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Linde Rangsarve, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701486</v>
+        <v>701698</v>
       </c>
       <c r="R46" t="n">
-        <v>6359900</v>
+        <v>6359959</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5672,12 +5650,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5686,56 +5674,55 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89807817</t>
+          <t>https://artportalen.se/Sighting/137291988</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13185284</v>
+        <v>69178532</v>
       </c>
       <c r="B47" t="n">
-        <v>43467</v>
+        <v>89143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101242</v>
+        <v>4405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5743,24 +5730,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701342</v>
+        <v>701531</v>
       </c>
       <c r="R47" t="n">
-        <v>6360057</v>
+        <v>6360078</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5779,17 +5766,17 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2006-06-30</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2006-06-30</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5804,82 +5791,68 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13185284</t>
+          <t>https://artportalen.se/Sighting/69178532</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68588838</v>
+        <v>137417622</v>
       </c>
       <c r="B48" t="n">
-        <v>43467</v>
+        <v>91623</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101242</v>
+        <v>5735</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>701415</v>
+        <v>701631</v>
       </c>
       <c r="R48" t="n">
-        <v>6359952</v>
+        <v>6360086</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5898,17 +5871,27 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,92 +5900,75 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588838</t>
+          <t>https://artportalen.se/Sighting/137417622</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68588850</v>
+        <v>137417978</v>
       </c>
       <c r="B49" t="n">
-        <v>43467</v>
+        <v>91623</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101242</v>
+        <v>5735</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>701382</v>
+        <v>701631</v>
       </c>
       <c r="R49" t="n">
-        <v>6360003</v>
+        <v>6360082</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6021,17 +5987,17 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,89 +6006,80 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588850</t>
+          <t>https://artportalen.se/Sighting/137417978</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>68588873</v>
+        <v>89807817</v>
       </c>
       <c r="B50" t="n">
-        <v>43467</v>
+        <v>92567</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101242</v>
+        <v>6031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>701378</v>
+        <v>701486</v>
       </c>
       <c r="R50" t="n">
-        <v>6360008</v>
+        <v>6359900</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6144,17 +6101,17 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,34 +6120,31 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68588873</t>
+          <t>https://artportalen.se/Sighting/89807817</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73899486</v>
+        <v>13185284</v>
       </c>
       <c r="B51" t="n">
         <v>43467</v>
@@ -6220,12 +6174,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6233,22 +6182,19 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>701392</v>
+        <v>701342</v>
       </c>
       <c r="R51" t="n">
-        <v>6359989</v>
+        <v>6360057</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6272,12 +6218,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2006-06-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,35 +6232,30 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899486</t>
+          <t>https://artportalen.se/Sighting/13185284</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73899493</v>
+        <v>68588838</v>
       </c>
       <c r="B52" t="n">
         <v>43467</v>
@@ -6344,7 +6285,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6366,10 +6307,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>701372</v>
+        <v>701415</v>
       </c>
       <c r="R52" t="n">
-        <v>6360022</v>
+        <v>6359952</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6396,12 +6337,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,7 +6351,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6432,13 +6372,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899493</t>
+          <t>https://artportalen.se/Sighting/68588838</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73899494</v>
+        <v>68588850</v>
       </c>
       <c r="B53" t="n">
         <v>43467</v>
@@ -6468,7 +6408,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6490,10 +6430,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701365</v>
+        <v>701382</v>
       </c>
       <c r="R53" t="n">
-        <v>6360025</v>
+        <v>6360003</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6520,12 +6460,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6534,7 +6474,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6556,13 +6495,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899494</t>
+          <t>https://artportalen.se/Sighting/68588850</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73899497</v>
+        <v>68588873</v>
       </c>
       <c r="B54" t="n">
         <v>43467</v>
@@ -6592,7 +6531,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6614,10 +6553,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701336</v>
+        <v>701378</v>
       </c>
       <c r="R54" t="n">
-        <v>6360054</v>
+        <v>6360008</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6644,12 +6583,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6658,7 +6597,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6680,13 +6618,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73899497</t>
+          <t>https://artportalen.se/Sighting/68588873</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80433370</v>
+        <v>73899486</v>
       </c>
       <c r="B55" t="n">
         <v>43467</v>
@@ -6716,7 +6654,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6734,17 +6672,17 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rambasvägen, Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701390</v>
+        <v>701392</v>
       </c>
       <c r="R55" t="n">
-        <v>6360006</v>
+        <v>6359989</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6768,12 +6706,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6804,13 +6742,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80433370</t>
+          <t>https://artportalen.se/Sighting/73899486</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80433374</v>
+        <v>73899493</v>
       </c>
       <c r="B56" t="n">
         <v>43467</v>
@@ -6840,7 +6778,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6858,17 +6796,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rambasvägen, Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701343</v>
+        <v>701372</v>
       </c>
       <c r="R56" t="n">
-        <v>6360056</v>
+        <v>6360022</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6892,12 +6830,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6928,13 +6866,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80433374</t>
+          <t>https://artportalen.se/Sighting/73899493</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>88866504</v>
+        <v>73899494</v>
       </c>
       <c r="B57" t="n">
         <v>43467</v>
@@ -6964,10 +6902,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -6982,10 +6924,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701368</v>
+        <v>701365</v>
       </c>
       <c r="R57" t="n">
-        <v>6360019</v>
+        <v>6360025</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7012,12 +6954,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7048,13 +6990,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88866504</t>
+          <t>https://artportalen.se/Sighting/73899494</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>95822713</v>
+        <v>73899497</v>
       </c>
       <c r="B58" t="n">
         <v>43467</v>
@@ -7084,10 +7026,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -7102,10 +7048,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701325</v>
+        <v>701336</v>
       </c>
       <c r="R58" t="n">
-        <v>6360075</v>
+        <v>6360054</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7132,12 +7078,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7168,13 +7114,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95822713</t>
+          <t>https://artportalen.se/Sighting/73899497</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111836843</v>
+        <v>80433370</v>
       </c>
       <c r="B59" t="n">
         <v>43467</v>
@@ -7207,7 +7153,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -7218,14 +7168,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701392</v>
+        <v>701390</v>
       </c>
       <c r="R59" t="n">
-        <v>6359993</v>
+        <v>6360006</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7252,12 +7202,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7288,13 +7238,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111836843</t>
+          <t>https://artportalen.se/Sighting/80433370</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111836851</v>
+        <v>80433374</v>
       </c>
       <c r="B60" t="n">
         <v>43467</v>
@@ -7324,10 +7274,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -7338,17 +7292,17 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>6. Rambasvägen, Gtl</t>
+          <t>Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>701368</v>
+        <v>701343</v>
       </c>
       <c r="R60" t="n">
-        <v>6360029</v>
+        <v>6360056</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7372,12 +7326,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7408,13 +7362,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111836851</t>
+          <t>https://artportalen.se/Sighting/80433374</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118077428</v>
+        <v>88866504</v>
       </c>
       <c r="B61" t="n">
         <v>43467</v>
@@ -7444,7 +7398,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -7462,10 +7416,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>701334</v>
+        <v>701368</v>
       </c>
       <c r="R61" t="n">
-        <v>6360070</v>
+        <v>6360019</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7492,12 +7446,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7528,13 +7482,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118077428</t>
+          <t>https://artportalen.se/Sighting/88866504</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126992416</v>
+        <v>95822713</v>
       </c>
       <c r="B62" t="n">
         <v>43467</v>
@@ -7564,7 +7518,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -7582,13 +7536,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701441</v>
+        <v>701325</v>
       </c>
       <c r="R62" t="n">
-        <v>6359878</v>
+        <v>6360075</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7612,12 +7566,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7648,13 +7602,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992416</t>
+          <t>https://artportalen.se/Sighting/95822713</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126992433</v>
+        <v>111836843</v>
       </c>
       <c r="B63" t="n">
         <v>43467</v>
@@ -7702,10 +7656,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>701364</v>
+        <v>701392</v>
       </c>
       <c r="R63" t="n">
-        <v>6360029</v>
+        <v>6359993</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7732,12 +7686,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7768,13 +7722,13 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992433</t>
+          <t>https://artportalen.se/Sighting/111836843</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126992447</v>
+        <v>111836851</v>
       </c>
       <c r="B64" t="n">
         <v>43467</v>
@@ -7804,7 +7758,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -7822,13 +7776,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701335</v>
+        <v>701368</v>
       </c>
       <c r="R64" t="n">
-        <v>6360059</v>
+        <v>6360029</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7852,12 +7806,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7888,38 +7842,38 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126992447</t>
+          <t>https://artportalen.se/Sighting/111836851</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129317243</v>
+        <v>118077428</v>
       </c>
       <c r="B65" t="n">
-        <v>43299</v>
+        <v>43467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101260</v>
+        <v>101242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7927,31 +7881,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>701618</v>
+        <v>701334</v>
       </c>
       <c r="R65" t="n">
-        <v>6359923</v>
+        <v>6360070</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7973,17 +7921,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7992,85 +7940,89 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Grustag med rikt av backtimjan.</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317243</t>
+          <t>https://artportalen.se/Sighting/118077428</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120308094</v>
+        <v>126992416</v>
       </c>
       <c r="B66" t="n">
-        <v>99093</v>
+        <v>43467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701557</v>
+        <v>701441</v>
       </c>
       <c r="R66" t="n">
-        <v>6360196</v>
+        <v>6359878</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8089,17 +8041,17 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8108,76 +8060,89 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308094</t>
+          <t>https://artportalen.se/Sighting/126992416</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137291989</v>
+        <v>126992433</v>
       </c>
       <c r="B67" t="n">
-        <v>99441</v>
+        <v>43467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701700</v>
+        <v>701364</v>
       </c>
       <c r="R67" t="n">
-        <v>6359961</v>
+        <v>6360029</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8196,27 +8161,17 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8225,33 +8180,38 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291989</t>
+          <t>https://artportalen.se/Sighting/126992433</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120308078</v>
+        <v>126992447</v>
       </c>
       <c r="B68" t="n">
-        <v>104640</v>
+        <v>43467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8259,37 +8219,50 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>6. Rambasvägen, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>701622</v>
+        <v>701335</v>
       </c>
       <c r="R68" t="n">
-        <v>6360225</v>
+        <v>6360059</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8308,17 +8281,17 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8327,76 +8300,95 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308078</t>
+          <t>https://artportalen.se/Sighting/126992447</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120308121</v>
+        <v>129317243</v>
       </c>
       <c r="B69" t="n">
-        <v>104640</v>
+        <v>43299</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220164</v>
+        <v>101260</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>701398</v>
+        <v>701618</v>
       </c>
       <c r="R69" t="n">
-        <v>6360004</v>
+        <v>6359923</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8420,12 +8412,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8439,7 +8431,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mot körvägkant..</t>
+          <t>Grustag med rikt av backtimjan.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8450,49 +8442,49 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308121</t>
+          <t>https://artportalen.se/Sighting/129317243</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120308124</v>
+        <v>120308094</v>
       </c>
       <c r="B70" t="n">
-        <v>109815</v>
+        <v>99093</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220204</v>
+        <v>219797</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8506,13 +8498,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701398</v>
+        <v>701557</v>
       </c>
       <c r="R70" t="n">
-        <v>6360004</v>
+        <v>6360196</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8555,7 +8547,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mot körvägkant..</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8572,51 +8564,51 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308124</t>
+          <t>https://artportalen.se/Sighting/120308094</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120308042</v>
+        <v>137291989</v>
       </c>
       <c r="B71" t="n">
-        <v>110078</v>
+        <v>99441</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>701451</v>
+        <v>701700</v>
       </c>
       <c r="R71" t="n">
-        <v>6359994</v>
+        <v>6359961</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8643,12 +8635,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8659,36 +8661,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308042</t>
+          <t>https://artportalen.se/Sighting/137291989</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120308086</v>
+        <v>120308078</v>
       </c>
       <c r="B72" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8696,21 +8693,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8720,13 +8717,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>701557</v>
+        <v>701622</v>
       </c>
       <c r="R72" t="n">
-        <v>6360196</v>
+        <v>6360225</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8769,7 +8766,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8786,16 +8783,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308086</t>
+          <t>https://artportalen.se/Sighting/120308078</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120308105</v>
+        <v>120308121</v>
       </c>
       <c r="B73" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8803,43 +8800,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>701480</v>
+        <v>701398</v>
       </c>
       <c r="R73" t="n">
-        <v>6360120</v>
+        <v>6360004</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8885,7 +8873,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8902,16 +8890,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308105</t>
+          <t>https://artportalen.se/Sighting/120308121</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120308043</v>
+        <v>120308124</v>
       </c>
       <c r="B74" t="n">
-        <v>107517</v>
+        <v>109815</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8919,16 +8907,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8936,20 +8924,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701451</v>
+        <v>701398</v>
       </c>
       <c r="R74" t="n">
-        <v>6359994</v>
+        <v>6360004</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8992,7 +8989,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog mot körvägkant..</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9009,16 +9006,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308043</t>
+          <t>https://artportalen.se/Sighting/120308124</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120308052</v>
+        <v>120308042</v>
       </c>
       <c r="B75" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,16 +9023,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9050,10 +9047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701467</v>
+        <v>701451</v>
       </c>
       <c r="R75" t="n">
-        <v>6359951</v>
+        <v>6359994</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9116,16 +9113,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308052</t>
+          <t>https://artportalen.se/Sighting/120308042</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120308053</v>
+        <v>120308086</v>
       </c>
       <c r="B76" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9133,16 +9130,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9157,13 +9154,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>701497</v>
+        <v>701557</v>
       </c>
       <c r="R76" t="n">
-        <v>6359955</v>
+        <v>6360196</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9206,7 +9203,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9223,16 +9220,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308053</t>
+          <t>https://artportalen.se/Sighting/120308086</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120308055</v>
+        <v>120308105</v>
       </c>
       <c r="B77" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9240,16 +9237,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9257,20 +9254,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>701519</v>
+        <v>701480</v>
       </c>
       <c r="R77" t="n">
-        <v>6359965</v>
+        <v>6360120</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9313,7 +9319,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9330,13 +9336,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308055</t>
+          <t>https://artportalen.se/Sighting/120308105</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120308059</v>
+        <v>120308043</v>
       </c>
       <c r="B78" t="n">
         <v>107517</v>
@@ -9371,10 +9377,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701524</v>
+        <v>701451</v>
       </c>
       <c r="R78" t="n">
-        <v>6359992</v>
+        <v>6359994</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9420,7 +9426,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9437,13 +9443,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308059</t>
+          <t>https://artportalen.se/Sighting/120308043</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120308060</v>
+        <v>120308052</v>
       </c>
       <c r="B79" t="n">
         <v>107517</v>
@@ -9478,10 +9484,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701526</v>
+        <v>701467</v>
       </c>
       <c r="R79" t="n">
-        <v>6360046</v>
+        <v>6359951</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9544,13 +9550,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308060</t>
+          <t>https://artportalen.se/Sighting/120308052</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120308062</v>
+        <v>120308053</v>
       </c>
       <c r="B80" t="n">
         <v>107517</v>
@@ -9585,10 +9591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>701524</v>
+        <v>701497</v>
       </c>
       <c r="R80" t="n">
-        <v>6360079</v>
+        <v>6359955</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9651,13 +9657,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308062</t>
+          <t>https://artportalen.se/Sighting/120308053</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120308063</v>
+        <v>120308055</v>
       </c>
       <c r="B81" t="n">
         <v>107517</v>
@@ -9692,10 +9698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701532</v>
+        <v>701519</v>
       </c>
       <c r="R81" t="n">
-        <v>6360141</v>
+        <v>6359965</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9758,13 +9764,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308063</t>
+          <t>https://artportalen.se/Sighting/120308055</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120308066</v>
+        <v>120308059</v>
       </c>
       <c r="B82" t="n">
         <v>107517</v>
@@ -9799,10 +9805,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701560</v>
+        <v>701524</v>
       </c>
       <c r="R82" t="n">
-        <v>6360140</v>
+        <v>6359992</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9837,11 +9843,6 @@
           <t>2024-07-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Mot S tallplantage?</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9853,7 +9854,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall). Vid rävgryt, grusigt.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9870,13 +9871,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308066</t>
+          <t>https://artportalen.se/Sighting/120308059</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120308067</v>
+        <v>120308060</v>
       </c>
       <c r="B83" t="n">
         <v>107517</v>
@@ -9911,10 +9912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>701574</v>
+        <v>701526</v>
       </c>
       <c r="R83" t="n">
-        <v>6360140</v>
+        <v>6360046</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9960,7 +9961,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9977,13 +9978,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308067</t>
+          <t>https://artportalen.se/Sighting/120308060</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120308068</v>
+        <v>120308062</v>
       </c>
       <c r="B84" t="n">
         <v>107517</v>
@@ -10018,13 +10019,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701594</v>
+        <v>701524</v>
       </c>
       <c r="R84" t="n">
-        <v>6360147</v>
+        <v>6360079</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10067,7 +10068,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10084,13 +10085,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308068</t>
+          <t>https://artportalen.se/Sighting/120308062</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120308071</v>
+        <v>120308063</v>
       </c>
       <c r="B85" t="n">
         <v>107517</v>
@@ -10125,10 +10126,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701636</v>
+        <v>701532</v>
       </c>
       <c r="R85" t="n">
-        <v>6360182</v>
+        <v>6360141</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10174,7 +10175,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog på åsrygg (relikt strandvall).</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10191,13 +10192,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308071</t>
+          <t>https://artportalen.se/Sighting/120308063</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120308076</v>
+        <v>120308066</v>
       </c>
       <c r="B86" t="n">
         <v>107517</v>
@@ -10232,10 +10233,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701638</v>
+        <v>701560</v>
       </c>
       <c r="R86" t="n">
-        <v>6360226</v>
+        <v>6360140</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10257,7 +10258,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10270,6 +10271,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Mot S tallplantage?</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10281,7 +10287,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta i gränsgata.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10298,13 +10304,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308076</t>
+          <t>https://artportalen.se/Sighting/120308066</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120308080</v>
+        <v>120308067</v>
       </c>
       <c r="B87" t="n">
         <v>107517</v>
@@ -10339,10 +10345,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701606</v>
+        <v>701574</v>
       </c>
       <c r="R87" t="n">
-        <v>6360224</v>
+        <v>6360140</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10405,13 +10411,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308080</t>
+          <t>https://artportalen.se/Sighting/120308067</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120308092</v>
+        <v>120308068</v>
       </c>
       <c r="B88" t="n">
         <v>107517</v>
@@ -10446,13 +10452,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701557</v>
+        <v>701594</v>
       </c>
       <c r="R88" t="n">
-        <v>6360196</v>
+        <v>6360147</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10495,7 +10501,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10512,13 +10518,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308092</t>
+          <t>https://artportalen.se/Sighting/120308068</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120308100</v>
+        <v>120308071</v>
       </c>
       <c r="B89" t="n">
         <v>107517</v>
@@ -10553,13 +10559,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>701541</v>
+        <v>701636</v>
       </c>
       <c r="R89" t="n">
-        <v>6360151</v>
+        <v>6360182</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10602,7 +10608,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10619,13 +10625,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308100</t>
+          <t>https://artportalen.se/Sighting/120308071</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120308102</v>
+        <v>120308076</v>
       </c>
       <c r="B90" t="n">
         <v>107517</v>
@@ -10660,13 +10666,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>701532</v>
+        <v>701638</v>
       </c>
       <c r="R90" t="n">
-        <v>6360143</v>
+        <v>6360226</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10685,7 +10691,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -10709,7 +10715,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10726,13 +10732,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308102</t>
+          <t>https://artportalen.se/Sighting/120308076</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120308106</v>
+        <v>120308080</v>
       </c>
       <c r="B91" t="n">
         <v>107517</v>
@@ -10767,13 +10773,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>701480</v>
+        <v>701606</v>
       </c>
       <c r="R91" t="n">
-        <v>6360120</v>
+        <v>6360224</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10816,7 +10822,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10833,13 +10839,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308106</t>
+          <t>https://artportalen.se/Sighting/120308080</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120308107</v>
+        <v>120308092</v>
       </c>
       <c r="B92" t="n">
         <v>107517</v>
@@ -10874,13 +10880,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>701452</v>
+        <v>701557</v>
       </c>
       <c r="R92" t="n">
-        <v>6360109</v>
+        <v>6360196</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10940,13 +10946,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308107</t>
+          <t>https://artportalen.se/Sighting/120308092</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120308109</v>
+        <v>120308100</v>
       </c>
       <c r="B93" t="n">
         <v>107517</v>
@@ -10981,13 +10987,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>701431</v>
+        <v>701541</v>
       </c>
       <c r="R93" t="n">
-        <v>6360091</v>
+        <v>6360151</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11047,13 +11053,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308109</t>
+          <t>https://artportalen.se/Sighting/120308100</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120308110</v>
+        <v>120308102</v>
       </c>
       <c r="B94" t="n">
         <v>107517</v>
@@ -11088,13 +11094,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>701423</v>
+        <v>701532</v>
       </c>
       <c r="R94" t="n">
-        <v>6360088</v>
+        <v>6360143</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11154,13 +11160,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308110</t>
+          <t>https://artportalen.se/Sighting/120308102</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120308112</v>
+        <v>120308106</v>
       </c>
       <c r="B95" t="n">
         <v>107517</v>
@@ -11195,13 +11201,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>701407</v>
+        <v>701480</v>
       </c>
       <c r="R95" t="n">
-        <v>6360080</v>
+        <v>6360120</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11261,13 +11267,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308112</t>
+          <t>https://artportalen.se/Sighting/120308106</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120308122</v>
+        <v>120308107</v>
       </c>
       <c r="B96" t="n">
         <v>107517</v>
@@ -11302,10 +11308,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>701398</v>
+        <v>701452</v>
       </c>
       <c r="R96" t="n">
-        <v>6360004</v>
+        <v>6360109</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11351,7 +11357,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkbarrskog mot körvägkant..</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11368,16 +11374,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308122</t>
+          <t>https://artportalen.se/Sighting/120308107</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129317272</v>
+        <v>120308109</v>
       </c>
       <c r="B97" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11409,13 +11415,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>701618</v>
+        <v>701431</v>
       </c>
       <c r="R97" t="n">
-        <v>6359923</v>
+        <v>6360091</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11439,12 +11445,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11458,7 +11464,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Grustag.</t>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11469,71 +11475,60 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317272</t>
+          <t>https://artportalen.se/Sighting/120308109</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>89823813</v>
+        <v>120308110</v>
       </c>
       <c r="B98" t="n">
-        <v>87291</v>
+        <v>107517</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>248955</v>
+        <v>221849</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>701391</v>
+        <v>701423</v>
       </c>
       <c r="R98" t="n">
-        <v>6359996</v>
+        <v>6360088</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11552,17 +11547,17 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11571,69 +11566,73 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89823813</t>
+          <t>https://artportalen.se/Sighting/120308110</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137268893</v>
+        <v>120308112</v>
       </c>
       <c r="B99" t="n">
-        <v>87494</v>
+        <v>107517</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>701437</v>
+        <v>701407</v>
       </c>
       <c r="R99" t="n">
-        <v>6359977</v>
+        <v>6360080</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11660,22 +11659,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11686,69 +11675,74 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest tall enstaka gran, mycket ljung, enbuskar.</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268893</t>
+          <t>https://artportalen.se/Sighting/120308112</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137268896</v>
+        <v>120308122</v>
       </c>
       <c r="B100" t="n">
-        <v>87494</v>
+        <v>107517</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>701505</v>
+        <v>701398</v>
       </c>
       <c r="R100" t="n">
-        <v>6360156</v>
+        <v>6360004</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11772,22 +11766,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>12:04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>12:04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11798,66 +11782,71 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog mot körvägkant..</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268896</t>
+          <t>https://artportalen.se/Sighting/120308122</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137268902</v>
+        <v>129317272</v>
       </c>
       <c r="B101" t="n">
-        <v>87494</v>
+        <v>107516</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>701632</v>
+        <v>701618</v>
       </c>
       <c r="R101" t="n">
-        <v>6360096</v>
+        <v>6359923</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11884,22 +11873,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11910,31 +11889,36 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Grustag.</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268902</t>
+          <t>https://artportalen.se/Sighting/129317272</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137270002</v>
+        <v>89823813</v>
       </c>
       <c r="B102" t="n">
-        <v>87494</v>
+        <v>87291</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11942,37 +11926,48 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>701481</v>
+        <v>701391</v>
       </c>
       <c r="R102" t="n">
-        <v>6359978</v>
+        <v>6359996</v>
       </c>
       <c r="S102" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11991,27 +11986,17 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2020-11-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2020-11-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12020,30 +12005,31 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270002</t>
+          <t>https://artportalen.se/Sighting/89823813</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137271098</v>
+        <v>137268893</v>
       </c>
       <c r="B103" t="n">
         <v>87494</v>
@@ -12074,14 +12060,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>701484</v>
+        <v>701437</v>
       </c>
       <c r="R103" t="n">
-        <v>6359923</v>
+        <v>6359977</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12113,7 +12099,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12123,7 +12109,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12138,24 +12124,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271098</t>
+          <t>https://artportalen.se/Sighting/137268893</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137271110</v>
+        <v>137268896</v>
       </c>
       <c r="B104" t="n">
         <v>87494</v>
@@ -12186,14 +12172,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>701553</v>
+        <v>701505</v>
       </c>
       <c r="R104" t="n">
-        <v>6359994</v>
+        <v>6360156</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12225,7 +12211,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12235,7 +12221,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12250,24 +12236,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271110</t>
+          <t>https://artportalen.se/Sighting/137268896</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137271118</v>
+        <v>137268902</v>
       </c>
       <c r="B105" t="n">
         <v>87494</v>
@@ -12298,17 +12284,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701619</v>
+        <v>701632</v>
       </c>
       <c r="R105" t="n">
-        <v>6359978</v>
+        <v>6360096</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12337,7 +12323,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12347,7 +12333,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12362,24 +12348,24 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271118</t>
+          <t>https://artportalen.se/Sighting/137268902</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137273092</v>
+        <v>137270002</v>
       </c>
       <c r="B106" t="n">
         <v>87494</v>
@@ -12414,13 +12400,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701412</v>
+        <v>701481</v>
       </c>
       <c r="R106" t="n">
-        <v>6360078</v>
+        <v>6359978</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12449,7 +12435,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12459,7 +12445,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12474,24 +12460,24 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273092</t>
+          <t>https://artportalen.se/Sighting/137270002</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137273103</v>
+        <v>137271098</v>
       </c>
       <c r="B107" t="n">
         <v>87494</v>
@@ -12522,14 +12508,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701648</v>
+        <v>701484</v>
       </c>
       <c r="R107" t="n">
-        <v>6360005</v>
+        <v>6359923</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12561,7 +12547,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12571,7 +12557,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12586,24 +12572,24 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273103</t>
+          <t>https://artportalen.se/Sighting/137271098</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>137313530</v>
+        <v>137271110</v>
       </c>
       <c r="B108" t="n">
         <v>87494</v>
@@ -12634,17 +12620,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701645</v>
+        <v>701553</v>
       </c>
       <c r="R108" t="n">
-        <v>6359988</v>
+        <v>6359994</v>
       </c>
       <c r="S108" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12668,22 +12654,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12698,74 +12684,65 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313530</t>
+          <t>https://artportalen.se/Sighting/137271110</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>69178541</v>
+        <v>137271118</v>
       </c>
       <c r="B109" t="n">
-        <v>87346</v>
+        <v>87494</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701531</v>
+        <v>701619</v>
       </c>
       <c r="R109" t="n">
-        <v>6360078</v>
+        <v>6359978</v>
       </c>
       <c r="S109" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12789,12 +12766,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12809,73 +12796,62 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69178541</t>
+          <t>https://artportalen.se/Sighting/137271118</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>89804386</v>
+        <v>137273092</v>
       </c>
       <c r="B110" t="n">
-        <v>87346</v>
+        <v>87494</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701357</v>
+        <v>701412</v>
       </c>
       <c r="R110" t="n">
-        <v>6360028</v>
+        <v>6360078</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12897,17 +12873,27 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12916,69 +12902,68 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf, Arne Pettersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89804386</t>
+          <t>https://artportalen.se/Sighting/137273092</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137268901</v>
+        <v>137273103</v>
       </c>
       <c r="B111" t="n">
-        <v>87578</v>
+        <v>87494</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
         <v>701648</v>
       </c>
       <c r="R111" t="n">
-        <v>6360091</v>
+        <v>6360005</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13010,7 +12995,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13020,7 +13005,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13029,72 +13014,71 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268901</t>
+          <t>https://artportalen.se/Sighting/137273103</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137271099</v>
+        <v>137313530</v>
       </c>
       <c r="B112" t="n">
-        <v>87578</v>
+        <v>87494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701497</v>
+        <v>701645</v>
       </c>
       <c r="R112" t="n">
-        <v>6359942</v>
+        <v>6359988</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13118,22 +13102,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13148,27 +13132,27 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271099</t>
+          <t>https://artportalen.se/Sighting/137313530</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137271101</v>
+        <v>69178541</v>
       </c>
       <c r="B113" t="n">
-        <v>87578</v>
+        <v>87346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13193,20 +13177,29 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701511</v>
+        <v>701531</v>
       </c>
       <c r="R113" t="n">
-        <v>6359954</v>
+        <v>6360078</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13230,22 +13223,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13260,27 +13243,27 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271101</t>
+          <t>https://artportalen.se/Sighting/69178541</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137271102</v>
+        <v>89804386</v>
       </c>
       <c r="B114" t="n">
-        <v>87578</v>
+        <v>87346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13305,20 +13288,31 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Gotlands högsta punkt norra, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>701503</v>
+        <v>701357</v>
       </c>
       <c r="R114" t="n">
-        <v>6359960</v>
+        <v>6360028</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13337,27 +13331,17 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13366,30 +13350,31 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ingrid Angelöf, Arne Pettersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271102</t>
+          <t>https://artportalen.se/Sighting/89804386</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137271104</v>
+        <v>137268901</v>
       </c>
       <c r="B115" t="n">
         <v>87578</v>
@@ -13420,17 +13405,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>701539</v>
+        <v>701648</v>
       </c>
       <c r="R115" t="n">
-        <v>6359971</v>
+        <v>6360091</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13459,7 +13444,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13469,7 +13454,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13478,30 +13463,31 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271104</t>
+          <t>https://artportalen.se/Sighting/137268901</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137271105</v>
+        <v>137271099</v>
       </c>
       <c r="B116" t="n">
         <v>87578</v>
@@ -13536,13 +13522,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>701536</v>
+        <v>701497</v>
       </c>
       <c r="R116" t="n">
-        <v>6359951</v>
+        <v>6359942</v>
       </c>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13571,7 +13557,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13581,7 +13567,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13607,13 +13593,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271105</t>
+          <t>https://artportalen.se/Sighting/137271099</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137271111</v>
+        <v>137271101</v>
       </c>
       <c r="B117" t="n">
         <v>87578</v>
@@ -13648,13 +13634,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>701561</v>
+        <v>701511</v>
       </c>
       <c r="R117" t="n">
-        <v>6360029</v>
+        <v>6359954</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13683,7 +13669,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13693,7 +13679,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13719,13 +13705,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271111</t>
+          <t>https://artportalen.se/Sighting/137271101</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137271114</v>
+        <v>137271102</v>
       </c>
       <c r="B118" t="n">
         <v>87578</v>
@@ -13760,13 +13746,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>701604</v>
+        <v>701503</v>
       </c>
       <c r="R118" t="n">
-        <v>6360076</v>
+        <v>6359960</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13795,7 +13781,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13805,7 +13791,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13831,13 +13817,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271114</t>
+          <t>https://artportalen.se/Sighting/137271102</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137271120</v>
+        <v>137271104</v>
       </c>
       <c r="B119" t="n">
         <v>87578</v>
@@ -13872,13 +13858,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701636</v>
+        <v>701539</v>
       </c>
       <c r="R119" t="n">
-        <v>6359977</v>
+        <v>6359971</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13907,7 +13893,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13917,7 +13903,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13943,13 +13929,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271120</t>
+          <t>https://artportalen.se/Sighting/137271104</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137271123</v>
+        <v>137271105</v>
       </c>
       <c r="B120" t="n">
         <v>87578</v>
@@ -13984,13 +13970,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701680</v>
+        <v>701536</v>
       </c>
       <c r="R120" t="n">
-        <v>6359996</v>
+        <v>6359951</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14019,7 +14005,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14029,7 +14015,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14055,13 +14041,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271123</t>
+          <t>https://artportalen.se/Sighting/137271105</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137271125</v>
+        <v>137271111</v>
       </c>
       <c r="B121" t="n">
         <v>87578</v>
@@ -14096,13 +14082,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701684</v>
+        <v>701561</v>
       </c>
       <c r="R121" t="n">
-        <v>6359985</v>
+        <v>6360029</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14131,7 +14117,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14141,7 +14127,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14167,13 +14153,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271125</t>
+          <t>https://artportalen.se/Sighting/137271111</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137273090</v>
+        <v>137271114</v>
       </c>
       <c r="B122" t="n">
         <v>87578</v>
@@ -14204,14 +14190,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701447</v>
+        <v>701604</v>
       </c>
       <c r="R122" t="n">
-        <v>6359950</v>
+        <v>6360076</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14243,7 +14229,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14253,7 +14239,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14262,31 +14248,30 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273090</t>
+          <t>https://artportalen.se/Sighting/137271114</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137273096</v>
+        <v>137271120</v>
       </c>
       <c r="B123" t="n">
         <v>87578</v>
@@ -14317,14 +14302,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701577</v>
+        <v>701636</v>
       </c>
       <c r="R123" t="n">
-        <v>6360063</v>
+        <v>6359977</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14356,7 +14341,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14366,7 +14351,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14375,31 +14360,30 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273096</t>
+          <t>https://artportalen.se/Sighting/137271120</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137273098</v>
+        <v>137271123</v>
       </c>
       <c r="B124" t="n">
         <v>87578</v>
@@ -14430,14 +14414,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701552</v>
+        <v>701680</v>
       </c>
       <c r="R124" t="n">
-        <v>6360025</v>
+        <v>6359996</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14469,7 +14453,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14479,7 +14463,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14488,31 +14472,30 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273098</t>
+          <t>https://artportalen.se/Sighting/137271123</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137273100</v>
+        <v>137271125</v>
       </c>
       <c r="B125" t="n">
         <v>87578</v>
@@ -14543,14 +14526,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701602</v>
+        <v>701684</v>
       </c>
       <c r="R125" t="n">
-        <v>6359969</v>
+        <v>6359985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14582,7 +14565,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14592,7 +14575,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14601,31 +14584,30 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273100</t>
+          <t>https://artportalen.se/Sighting/137271125</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137273104</v>
+        <v>137273090</v>
       </c>
       <c r="B126" t="n">
         <v>87578</v>
@@ -14660,10 +14642,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>701659</v>
+        <v>701447</v>
       </c>
       <c r="R126" t="n">
-        <v>6360008</v>
+        <v>6359950</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14695,7 +14677,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14705,7 +14687,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14732,13 +14714,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273104</t>
+          <t>https://artportalen.se/Sighting/137273090</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>137313528</v>
+        <v>137273096</v>
       </c>
       <c r="B127" t="n">
         <v>87578</v>
@@ -14773,13 +14755,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>701582</v>
+        <v>701577</v>
       </c>
       <c r="R127" t="n">
-        <v>6359972</v>
+        <v>6360063</v>
       </c>
       <c r="S127" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14803,22 +14785,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14834,65 +14816,65 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313528</t>
+          <t>https://artportalen.se/Sighting/137273096</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>137271117</v>
+        <v>137273098</v>
       </c>
       <c r="B128" t="n">
-        <v>87606</v>
+        <v>87578</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6052416</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>701617</v>
+        <v>701552</v>
       </c>
       <c r="R128" t="n">
-        <v>6359978</v>
+        <v>6360025</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14921,7 +14903,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14931,7 +14913,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14940,22 +14922,700 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273098</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>137273100</v>
+      </c>
+      <c r="B129" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>701602</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6359969</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273100</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>137273104</v>
+      </c>
+      <c r="B130" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>701659</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6360008</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273104</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>137313528</v>
+      </c>
+      <c r="B131" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>701582</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6359972</v>
+      </c>
+      <c r="S131" t="n">
+        <v>16</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137313528</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>137417394</v>
+      </c>
+      <c r="B132" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>701582</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6360111</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417394</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>137417396</v>
+      </c>
+      <c r="B133" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>701629</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6360133</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417396</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>137271117</v>
+      </c>
+      <c r="B134" t="n">
+        <v>87606</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Lojsta Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>701617</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6359978</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271117</t>
         </is>
@@ -15090,6 +15750,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87376</v>
+        <v>87387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87376</v>
+        <v>87387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137417962</v>
       </c>
       <c r="B27" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>137268891</v>
       </c>
       <c r="B28" t="n">
-        <v>90928</v>
+        <v>90939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137268899</v>
       </c>
       <c r="B29" t="n">
-        <v>90928</v>
+        <v>90939</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137270003</v>
       </c>
       <c r="B32" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>137291990</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137417983</v>
       </c>
       <c r="B35" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>137268897</v>
       </c>
       <c r="B37" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137271107</v>
       </c>
       <c r="B41" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137271121</v>
       </c>
       <c r="B42" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137271127</v>
       </c>
       <c r="B43" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>137273099</v>
       </c>
       <c r="B44" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137273105</v>
       </c>
       <c r="B45" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>137291988</v>
       </c>
       <c r="B46" t="n">
-        <v>89321</v>
+        <v>89332</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>137417622</v>
       </c>
       <c r="B48" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>137417978</v>
       </c>
       <c r="B49" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>137291989</v>
       </c>
       <c r="B71" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>137268893</v>
       </c>
       <c r="B103" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>137268896</v>
       </c>
       <c r="B104" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>137268902</v>
       </c>
       <c r="B105" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>137270002</v>
       </c>
       <c r="B106" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>137271098</v>
       </c>
       <c r="B107" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>137271110</v>
       </c>
       <c r="B108" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>137271118</v>
       </c>
       <c r="B109" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>137273092</v>
       </c>
       <c r="B110" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>137273103</v>
       </c>
       <c r="B111" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>137313530</v>
       </c>
       <c r="B112" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>137268901</v>
       </c>
       <c r="B115" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>137271099</v>
       </c>
       <c r="B116" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>137271101</v>
       </c>
       <c r="B117" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>137271102</v>
       </c>
       <c r="B118" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>137271104</v>
       </c>
       <c r="B119" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>137271105</v>
       </c>
       <c r="B120" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>137271111</v>
       </c>
       <c r="B121" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>137271114</v>
       </c>
       <c r="B122" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>137271120</v>
       </c>
       <c r="B123" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>137271123</v>
       </c>
       <c r="B124" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>137271125</v>
       </c>
       <c r="B125" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>137273090</v>
       </c>
       <c r="B126" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>137273096</v>
       </c>
       <c r="B127" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>137273098</v>
       </c>
       <c r="B128" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>137273100</v>
       </c>
       <c r="B129" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>137273104</v>
       </c>
       <c r="B130" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137313528</v>
       </c>
       <c r="B131" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>137417394</v>
       </c>
       <c r="B132" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>137417396</v>
       </c>
       <c r="B133" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>137271117</v>
       </c>
       <c r="B134" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87387</v>
+        <v>87388</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87387</v>
+        <v>87388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137417962</v>
       </c>
       <c r="B27" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>137268891</v>
       </c>
       <c r="B28" t="n">
-        <v>90939</v>
+        <v>90940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137268899</v>
       </c>
       <c r="B29" t="n">
-        <v>90939</v>
+        <v>90940</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137270003</v>
       </c>
       <c r="B32" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>137291990</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137417983</v>
       </c>
       <c r="B35" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>137268897</v>
       </c>
       <c r="B37" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137271107</v>
       </c>
       <c r="B41" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137271121</v>
       </c>
       <c r="B42" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137271127</v>
       </c>
       <c r="B43" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>137273099</v>
       </c>
       <c r="B44" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137273105</v>
       </c>
       <c r="B45" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>137291988</v>
       </c>
       <c r="B46" t="n">
-        <v>89332</v>
+        <v>89333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>137417622</v>
       </c>
       <c r="B48" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>137417978</v>
       </c>
       <c r="B49" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>137291989</v>
       </c>
       <c r="B71" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>137268893</v>
       </c>
       <c r="B103" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>137268896</v>
       </c>
       <c r="B104" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>137268902</v>
       </c>
       <c r="B105" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>137270002</v>
       </c>
       <c r="B106" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>137271098</v>
       </c>
       <c r="B107" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>137271110</v>
       </c>
       <c r="B108" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>137271118</v>
       </c>
       <c r="B109" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>137273092</v>
       </c>
       <c r="B110" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>137273103</v>
       </c>
       <c r="B111" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>137313530</v>
       </c>
       <c r="B112" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>137268901</v>
       </c>
       <c r="B115" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>137271099</v>
       </c>
       <c r="B116" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>137271101</v>
       </c>
       <c r="B117" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>137271102</v>
       </c>
       <c r="B118" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>137271104</v>
       </c>
       <c r="B119" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>137271105</v>
       </c>
       <c r="B120" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>137271111</v>
       </c>
       <c r="B121" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>137271114</v>
       </c>
       <c r="B122" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>137271120</v>
       </c>
       <c r="B123" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>137271123</v>
       </c>
       <c r="B124" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>137271125</v>
       </c>
       <c r="B125" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>137273090</v>
       </c>
       <c r="B126" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>137273096</v>
       </c>
       <c r="B127" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>137273098</v>
       </c>
       <c r="B128" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>137273100</v>
       </c>
       <c r="B129" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>137273104</v>
       </c>
       <c r="B130" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137313528</v>
       </c>
       <c r="B131" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>137417394</v>
       </c>
       <c r="B132" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>137417396</v>
       </c>
       <c r="B133" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>137271117</v>
       </c>
       <c r="B134" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87388</v>
+        <v>87391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87388</v>
+        <v>87391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137417962</v>
       </c>
       <c r="B27" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>137268891</v>
       </c>
       <c r="B28" t="n">
-        <v>90940</v>
+        <v>90943</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137268899</v>
       </c>
       <c r="B29" t="n">
-        <v>90940</v>
+        <v>90943</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137270003</v>
       </c>
       <c r="B32" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>137291990</v>
       </c>
       <c r="B34" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137417983</v>
       </c>
       <c r="B35" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>137268897</v>
       </c>
       <c r="B37" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137271107</v>
       </c>
       <c r="B41" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137271121</v>
       </c>
       <c r="B42" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137271127</v>
       </c>
       <c r="B43" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>137273099</v>
       </c>
       <c r="B44" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137273105</v>
       </c>
       <c r="B45" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>137291988</v>
       </c>
       <c r="B46" t="n">
-        <v>89333</v>
+        <v>89336</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>137417622</v>
       </c>
       <c r="B48" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>137417978</v>
       </c>
       <c r="B49" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>137291989</v>
       </c>
       <c r="B71" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>137268893</v>
       </c>
       <c r="B103" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>137268896</v>
       </c>
       <c r="B104" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>137268902</v>
       </c>
       <c r="B105" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>137270002</v>
       </c>
       <c r="B106" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>137271098</v>
       </c>
       <c r="B107" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>137271110</v>
       </c>
       <c r="B108" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>137271118</v>
       </c>
       <c r="B109" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>137273092</v>
       </c>
       <c r="B110" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>137273103</v>
       </c>
       <c r="B111" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>137313530</v>
       </c>
       <c r="B112" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>137268901</v>
       </c>
       <c r="B115" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>137271099</v>
       </c>
       <c r="B116" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>137271101</v>
       </c>
       <c r="B117" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>137271102</v>
       </c>
       <c r="B118" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>137271104</v>
       </c>
       <c r="B119" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>137271105</v>
       </c>
       <c r="B120" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>137271111</v>
       </c>
       <c r="B121" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>137271114</v>
       </c>
       <c r="B122" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>137271120</v>
       </c>
       <c r="B123" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>137271123</v>
       </c>
       <c r="B124" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>137271125</v>
       </c>
       <c r="B125" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>137273090</v>
       </c>
       <c r="B126" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>137273096</v>
       </c>
       <c r="B127" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>137273098</v>
       </c>
       <c r="B128" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>137273100</v>
       </c>
       <c r="B129" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>137273104</v>
       </c>
       <c r="B130" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137313528</v>
       </c>
       <c r="B131" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>137417394</v>
       </c>
       <c r="B132" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>137417396</v>
       </c>
       <c r="B133" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>137271117</v>
       </c>
       <c r="B134" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 62551-2022 artfynd.xlsx
+++ b/artfynd/A 62551-2022 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>137271100</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137271126</v>
       </c>
       <c r="B5" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137273106</v>
       </c>
       <c r="B6" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137278117</v>
       </c>
       <c r="B7" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137335983</v>
       </c>
       <c r="B8" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137271106</v>
       </c>
       <c r="B10" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137271124</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137268894</v>
       </c>
       <c r="B14" t="n">
-        <v>87391</v>
+        <v>87395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137271097</v>
       </c>
       <c r="B15" t="n">
-        <v>87391</v>
+        <v>87395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137268895</v>
       </c>
       <c r="B17" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137268900</v>
       </c>
       <c r="B18" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137269999</v>
       </c>
       <c r="B19" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>137270001</v>
       </c>
       <c r="B20" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137270004</v>
       </c>
       <c r="B21" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137270007</v>
       </c>
       <c r="B22" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137273093</v>
       </c>
       <c r="B23" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137273095</v>
       </c>
       <c r="B24" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137287620</v>
       </c>
       <c r="B25" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137291987</v>
       </c>
       <c r="B26" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>137417962</v>
       </c>
       <c r="B27" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>137268891</v>
       </c>
       <c r="B28" t="n">
-        <v>90943</v>
+        <v>90947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137268899</v>
       </c>
       <c r="B29" t="n">
-        <v>90943</v>
+        <v>90947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137270003</v>
       </c>
       <c r="B32" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>137291990</v>
       </c>
       <c r="B34" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137417983</v>
       </c>
       <c r="B35" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>137268897</v>
       </c>
       <c r="B37" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137271107</v>
       </c>
       <c r="B41" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137271121</v>
       </c>
       <c r="B42" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137271127</v>
       </c>
       <c r="B43" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>137273099</v>
       </c>
       <c r="B44" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137273105</v>
       </c>
       <c r="B45" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>137291988</v>
       </c>
       <c r="B46" t="n">
-        <v>89336</v>
+        <v>89340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>137417622</v>
       </c>
       <c r="B48" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>137417978</v>
       </c>
       <c r="B49" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>137291989</v>
       </c>
       <c r="B71" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>137268893</v>
       </c>
       <c r="B103" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>137268896</v>
       </c>
       <c r="B104" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>137268902</v>
       </c>
       <c r="B105" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>137270002</v>
       </c>
       <c r="B106" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>137271098</v>
       </c>
       <c r="B107" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>137271110</v>
       </c>
       <c r="B108" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>137271118</v>
       </c>
       <c r="B109" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>137273092</v>
       </c>
       <c r="B110" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>137273103</v>
       </c>
       <c r="B111" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>137313530</v>
       </c>
       <c r="B112" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>137268901</v>
       </c>
       <c r="B115" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>137271099</v>
       </c>
       <c r="B116" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>137271101</v>
       </c>
       <c r="B117" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>137271102</v>
       </c>
       <c r="B118" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>137271104</v>
       </c>
       <c r="B119" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>137271105</v>
       </c>
       <c r="B120" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>137271111</v>
       </c>
       <c r="B121" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>137271114</v>
       </c>
       <c r="B122" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>137271120</v>
       </c>
       <c r="B123" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>137271123</v>
       </c>
       <c r="B124" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>137271125</v>
       </c>
       <c r="B125" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>137273090</v>
       </c>
       <c r="B126" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>137273096</v>
       </c>
       <c r="B127" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>137273098</v>
       </c>
       <c r="B128" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>137273100</v>
       </c>
       <c r="B129" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>137273104</v>
       </c>
       <c r="B130" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137313528</v>
       </c>
       <c r="B131" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>137417394</v>
       </c>
       <c r="B132" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>137417396</v>
       </c>
       <c r="B133" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>137271117</v>
       </c>
       <c r="B134" t="n">
-        <v>87621</v>
+        <v>87625</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
